--- a/ServiceNow_Discovery_ACC_Data_Inventory_JA.xlsx
+++ b/ServiceNow_Discovery_ACC_Data_Inventory_JA.xlsx
@@ -2,8 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery_ACCデータ一覧" sheetId="1" r:id="R6765876271ad4250"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP Rangeテーブル調査" sheetId="2" r:id="R93b90a31eb88440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery_ACCデータ一覧" sheetId="1" r:id="R759b1710ce9145e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP Rangeテーブル調査" sheetId="2" r:id="R98028f52e1664542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4方式横断比較" sheetId="3" r:id="R5b7242274a154d77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中分類の分類基準" sheetId="4" r:id="R96e3a6555a3147fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="19">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -123,8 +125,19 @@
       <x:color rgb="FF604C00"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF604C00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="38">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -226,6 +239,91 @@
         <x:fgColor rgb="FFEDEDED"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F5597"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDEDED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F5597"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDEDED"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -275,7 +373,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="110">
+  <x:cellXfs count="187">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -553,6 +651,193 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="18" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="28" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="28" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="35" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="35" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="31" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="31" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="37" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="37" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="37" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="37" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -597,6 +882,53 @@
     <x:tableColumn id="10" name="官方资料标题"/>
     <x:tableColumn id="11" name="官方 URL"/>
     <x:tableColumn id="12" name="辅助资料 / 第二依据"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FourWayTableInventory" displayName="FourWayTableInventory" ref="A24:H51" headerRowCount="1">
+  <x:autoFilter ref="A24:H51"/>
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="大分类"/>
+    <x:tableColumn id="2" name="表组"/>
+    <x:tableColumn id="3" name="主要物理表"/>
+    <x:tableColumn id="4" name="读写性质"/>
+    <x:tableColumn id="5" name="主要作用"/>
+    <x:tableColumn id="6" name="独有 / 重叠"/>
+    <x:tableColumn id="7" name="区别与注意事项"/>
+    <x:tableColumn id="8" name="官方参考"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FourWayScenarioGuide" displayName="FourWayScenarioGuide" ref="A54:E65" headerRowCount="1">
+  <x:autoFilter ref="A54:E65"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="实际场景"/>
+    <x:tableColumn id="2" name="首选方式"/>
+    <x:tableColumn id="3" name="补充方式"/>
+    <x:tableColumn id="4" name="选择理由"/>
+    <x:tableColumn id="5" name="实施注意"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ClassificationBasisJA" displayName="ClassificationBasisJA" ref="A13:G40" headerRowCount="1">
+  <x:autoFilter ref="A13:G40"/>
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="大分類"/>
+    <x:tableColumn id="2" name="中分類"/>
+    <x:tableColumn id="3" name="分類基準／対象"/>
+    <x:tableColumn id="4" name="公式上の位置付け"/>
+    <x:tableColumn id="5" name="本資料での用途"/>
+    <x:tableColumn id="6" name="解釈上の注意"/>
+    <x:tableColumn id="7" name="公式リファレンス"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -2227,7 +2559,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4d373527aa94755"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b99aa9c810e47bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4841,7 +5173,2622 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58342c4622b54e45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raff78537a47f4180"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36.25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="38.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48.130001068115234" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="A1" s="113" t="str">
+        <x:v>Horizontal Discovery / Cloud Discovery / Service Mapping / ACC 横断比較</x:v>
+      </x:c>
+      <x:c r="B1" s="113"/>
+      <x:c r="C1" s="113"/>
+      <x:c r="D1" s="113"/>
+      <x:c r="E1" s="113"/>
+      <x:c r="F1" s="113"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+    </x:row>
+    <x:row r="2" ht="34.5" customHeight="1">
+      <x:c r="A2" s="117" t="str">
+        <x:v>結論：4方式は排他的な選択肢ではなく、階層的に補完し合う関係です。Horizontal Discovery、Cloud Discovery、ACC が基盤リソースの情報を作成・補完し、Service Mapping がそれらの CI を業務視点の Application Service と依存関係トポロジとして構成します。</x:v>
+      </x:c>
+      <x:c r="B2" s="117"/>
+      <x:c r="C2" s="117"/>
+      <x:c r="D2" s="117"/>
+      <x:c r="E2" s="117"/>
+      <x:c r="F2" s="117"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="3" ht="34.5" customHeight="1">
+      <x:c r="A3" s="121" t="str">
+        <x:v>テーブルの記載方針：代表的かつ安定しており、アーキテクチャ判断に有用なテーブルを掲載しています。製品 Pattern、プラグイン、CMDB CI Class Models は継続的に更新されるため、完全なオブジェクト単位の一覧は、前2シートおよび対象インスタンスの Pattern／Dictionary と併せて確認してください。作成日：2026-06-11。</x:v>
+      </x:c>
+      <x:c r="B3" s="121"/>
+      <x:c r="C3" s="121"/>
+      <x:c r="D3" s="121"/>
+      <x:c r="E3" s="121"/>
+      <x:c r="F3" s="121"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+    </x:row>
+    <x:row r="5" ht="31.5" customHeight="1">
+      <x:c r="A5" s="124" t="str">
+        <x:v>1. 機能・アーキテクチャ横断比較</x:v>
+      </x:c>
+      <x:c r="B5" s="124"/>
+      <x:c r="C5" s="124"/>
+      <x:c r="D5" s="124"/>
+      <x:c r="E5" s="124"/>
+      <x:c r="F5" s="124"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6" ht="31.5" customHeight="1">
+      <x:c r="A6" s="130" t="str">
+        <x:v>比較項目</x:v>
+      </x:c>
+      <x:c r="B6" s="130" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="C6" s="130" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="D6" s="130" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="E6" s="130" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="F6" s="130" t="str">
+        <x:v>横断的な結論／選定ポイント</x:v>
+      </x:c>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7" ht="64.5" customHeight="1">
+      <x:c r="A7" s="135" t="str">
+        <x:v>主な目的</x:v>
+      </x:c>
+      <x:c r="B7" s="131" t="str">
+        <x:v>ローカル/データ センター ネットワークをスキャンし、コンピューター、ネットワーク、ストレージ、仮想化、アプリケーション、データベースを特定し、基本的な CI と直接的な技術関係を確立します。</x:v>
+      </x:c>
+      <x:c r="C7" s="131" t="str">
+        <x:v>AWS/Azure/GCP/IBM/VMware などのクラウド API を使用して、アカウント、サブスクリプション、プロジェクト、リージョンごとにクラウド リソース、構成、タグをインベントリします。</x:v>
+      </x:c>
+      <x:c r="D7" s="131" t="str">
+        <x:v>技術的な CI をアプリケーション サービスに編成し、エントリ ポイント、タグ、フロー、または既存の CMDB から始まるエンドツーエンドの依存関係トポロジを形成します。</x:v>
+      </x:c>
+      <x:c r="E7" s="131" t="str">
+        <x:v>Windows/Linux/macOS などのエンドポイントにエージェントをインストールし、ホスト内からアセット、プロセス、接続、インジケーター、またはログをアクティブにレポートします。</x:v>
+      </x:c>
+      <x:c r="F7" s="136" t="str">
+        <x:v>これら 4 つは代替品ではありません。水平/クラウド/ACC は CI を確立または補完します。Service Mappingは、これらの CI を使用してビジネス サービス ビューを構築します。</x:v>
+      </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8" ht="64.5" customHeight="1">
+      <x:c r="A8" s="135" t="str">
+        <x:v>検出方向</x:v>
+      </x:c>
+      <x:c r="B8" s="131" t="str">
+        <x:v>水平: IP 範囲から外側に向かってインフラストラクチャ全体をスキャンします。</x:v>
+      </x:c>
+      <x:c r="C8" s="131" t="str">
+        <x:v>水平/アカウント レベル: クラウド アカウントまたはサービス アカウントから下方向にリソースを列挙します。</x:v>
+      </x:c>
+      <x:c r="D8" s="131" t="str">
+        <x:v>トップダウン: ビジネス ポータルまたはサービス定義から下方向に依存関係を追跡します。タグ、フロー、クエリベースの集計もサポートされています。</x:v>
+      </x:c>
+      <x:c r="E8" s="131" t="str">
+        <x:v>内部から外部へ、プッシュ: エージェントはホスト内部のデータを収集し、それを積極的に送信します。</x:v>
+      </x:c>
+      <x:c r="F8" s="136" t="str">
+        <x:v>方向によって目的が決まります。資産インベントリについては、「水平/クラウド/ACC」を参照してください。ビジネスへの影響とサービスの依存関係については、「Service Mapping」を参照してください。</x:v>
+      </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9" ht="64.5" customHeight="1">
+      <x:c r="A9" s="135" t="str">
+        <x:v>実行経路／通信方式</x:v>
+      </x:c>
+      <x:c r="B9" s="131" t="str">
+        <x:v>インスタンス → ECC キュー → MID Server → ターゲットデバイス。通常、MID はターゲットにアクティブに接続します。</x:v>
+      </x:c>
+      <x:c r="C9" s="131" t="str">
+        <x:v>インスタンス/MID Server → クラウド プロバイダー REST API。クラウド アカウントの権限と一時的な認証情報を使用します。</x:v>
+      </x:c>
+      <x:c r="D9" s="131" t="str">
+        <x:v>Discovery と MID Serverに依存します。Patternはサービス メンバーにアクセスし、検出された CI、プロセス、および TCP データも再利用します。</x:v>
+      </x:c>
+      <x:c r="E9" s="131" t="str">
+        <x:v>エージェント → WebSocket/MID Serverまたはサポートされている MID レス パス → インスタンス。通信はエンドポイントによってアクティブに開始されます。</x:v>
+      </x:c>
+      <x:c r="F9" s="136" t="str">
+        <x:v>厳格なファイアウォール環境やインバウンドスキャンを許可しない領域には ACC が適しています。クラウドのコントロールプレーン資産には Cloud Discovery を優先します。</x:v>
+      </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10" ht="64.5" customHeight="1">
+      <x:c r="A10" s="135" t="str">
+        <x:v>主な起点／対象範囲</x:v>
+      </x:c>
+      <x:c r="B10" s="131" t="str">
+        <x:v>Discovery Schedule、IP Range、IP List、Subnet、Behavior。</x:v>
+      </x:c>
+      <x:c r="C10" s="131" t="str">
+        <x:v>Cloud Account/Service Account、Subscription、Project、Region/Datacenter。</x:v>
+      </x:c>
+      <x:c r="D10" s="131" t="str">
+        <x:v>URL、IP:Port、Host、Application Entry Point、Cloud Tag、CMDB Query、TCP/Flow。</x:v>
+      </x:c>
+      <x:c r="E10" s="131" t="str">
+        <x:v>エージェント ポリシー、チェック、プラグイン、ホスト グループ、またはエージェントがインストールされているエンドポイント。</x:v>
+      </x:c>
+      <x:c r="F10" s="136" t="str">
+        <x:v>入り口が違うので、単純に「CMDBを書くかどうか」だけで製品の重複を判断することはできません。</x:v>
+      </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11" ht="64.5" customHeight="1">
+      <x:c r="A11" s="135" t="str">
+        <x:v>Agent の導入要否</x:v>
+      </x:c>
+      <x:c r="B11" s="131" t="str">
+        <x:v>必須ではありません。エージェントはいません。</x:v>
+      </x:c>
+      <x:c r="C11" s="131" t="str">
+        <x:v>通常、各クラウド ホストにエージェントをインストールする必要はありません。コントロール プレーンのメタデータはクラウド API を通じて取得されます。</x:v>
+      </x:c>
+      <x:c r="D11" s="131" t="str">
+        <x:v>通常、専用のエージェントは必要ありませんが、Discovery/MID はマップされたテクノロジー スタックにアクセスできる必要があります。 ACC が提供するホスト データを使用できます。</x:v>
+      </x:c>
+      <x:c r="E11" s="131" t="str">
+        <x:v>エージェントはターゲット エンドポイントにインストールして維持する必要があります。</x:v>
+      </x:c>
+      <x:c r="F11" s="136" t="str">
+        <x:v>大規模なサーバー環境は混在可能です。水平環境はカバレッジおよびネットワーク機器用、ACC は詳細なエンドポイント データ用です。</x:v>
+      </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12" ht="64.5" customHeight="1">
+      <x:c r="A12" s="135" t="str">
+        <x:v>権限／資格情報</x:v>
+      </x:c>
+      <x:c r="B12" s="131" t="str">
+        <x:v>SSH、SNMP、Windows/WMI/WinRM、JDBC、デバイス API などのターゲット資格情報。</x:v>
+      </x:c>
+      <x:c r="C12" s="131" t="str">
+        <x:v>各リソースの Cloud IAM ロール、サービス プリンシパル、サービス アカウント、API 権限。</x:v>
+      </x:c>
+      <x:c r="D12" s="131" t="str">
+        <x:v>Discovery から資格情報を継承し、アプリケーション、データベース、ロード バランサーなどの入力資格情報が必要になる場合があります。</x:v>
+      </x:c>
+      <x:c r="E12" s="131" t="str">
+        <x:v>エージェントはキー/証明書、ポリシー、およびチェック権限を登録します。大量のターゲット ログイン資格情報を MID から保存する必要性が軽減されます。</x:v>
+      </x:c>
+      <x:c r="F12" s="136" t="str">
+        <x:v>Cloud Discovery の権限が不十分だとリソースが漏洩します。水平/Service Mapping資格情報が不十分な場合、分類または浅い情報で停止します。</x:v>
+      </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13" ht="64.5" customHeight="1">
+      <x:c r="A13" s="135" t="str">
+        <x:v>取得データの深度</x:v>
+      </x:c>
+      <x:c r="B13" s="131" t="str">
+        <x:v>ハードウェア、OS、インターフェース、ソフトウェア、アプリケーション、データベース、およびネットワーク接続可能なデバイスの直接ホスティング関係。深さは資格情報とPatternによって異なります。</x:v>
+      </x:c>
+      <x:c r="C13" s="131" t="str">
+        <x:v>クラウド コントロール プレーンのメタデータは最も強力です。アカウント、リージョン、リソース グループ、VM、ネットワーク、ストレージ、データベース、負荷分散、ラベルなどです。通常、VM の内部 OS の深さとは等しくありません。</x:v>
+      </x:c>
+      <x:c r="D13" s="131" t="str">
+        <x:v>「誰が誰に依存するか」とサービスの境界に焦点を当てます。メンバー CI の属性の深さは、Discovery、Cloud Discovery、ACC、またはその他の CMDB ソースから取得されます。</x:v>
+      </x:c>
+      <x:c r="E13" s="131" t="str">
+        <x:v>ホストの強力な内部詳細: CPU/メモリ/OS、ファイル システム、ソフトウェアの証拠、実行中のプロセス、TCP、証明書、メトリック、ログ。</x:v>
+      </x:c>
+      <x:c r="F13" s="136" t="str">
+        <x:v>クラウド VM の完全なビューには通常、Cloud Discovery + horizo​​ntal または ACC が必要です。</x:v>
+      </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14" ht="64.5" customHeight="1">
+      <x:c r="A14" s="135" t="str">
+        <x:v>主なリレーション／トポロジ</x:v>
+      </x:c>
+      <x:c r="B14" s="131" t="str">
+        <x:v>実行、包含、ホストなどの CI 間に直接の技術的関係を作成します。ビジネス サービスの境界を理解していません。</x:v>
+      </x:c>
+      <x:c r="C14" s="131" t="str">
+        <x:v>クラウド レベルとリソース関係 (アカウント/リージョン/リソース グループ/ネットワーク/サブネット/VM/ディスク/LB など) を作成します。</x:v>
+      </x:c>
+      <x:c r="D14" s="131" t="str">
+        <x:v>アプリケーション サービスのメンバーシップとランタイムの依存関係の作成は、4 つの中で最もビジネスへの影響分析を重視したものです。</x:v>
+      </x:c>
+      <x:c r="E14" s="131" t="str">
+        <x:v>ホストコンポーネント、プロセス、TCP、アプリケーションなどの関係を更新します。それ自体は完全なアプリケーション サービス モデリングを置き換えるものではありません。</x:v>
+      </x:c>
+      <x:c r="F14" s="136" t="str">
+        <x:v>当局者は、ホリゾンタル社がビジネスサービスについて認識していないことを明らかにしている。Service Mappingは、技術トポロジをサービスの観点にアップグレードするために必要です。</x:v>
+      </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15" ht="120.75" customHeight="1">
+      <x:c r="A15" s="135" t="str">
+        <x:v>主な実行／制御テーブル</x:v>
+      </x:c>
+      <x:c r="B15" s="131" t="str">
+        <x:v>discovery_schedule
+discovery_range_item
+discovery_status
+discovery_device_history
+discovery_log
+ecc_queue
+ecc_agent
+discovery_credentials
+dscy_credentials_affinity</x:v>
+      </x:c>
+      <x:c r="C15" s="131" t="str">
+        <x:v>discovery_schedule
+discovery_status
+discovery_log
+ecc_queue
+ecc_agent
+sys_object_source
+cmdb_datasource_last_update
+(特定のクラウド アカウント構成テーブルはプロバイダー/プラグインによって変わります)</x:v>
+      </x:c>
+      <x:c r="D15" s="131" t="str">
+        <x:v>cmdb_ci_service_autoシステム 
+cmdb_running_process
+cmdb_tcp
+cmdb_key_value
+cmdb_rel_ci
+svc_ci_assoc
+(および Discovery/MID 操作レコードの再利用)</x:v>
+      </x:c>
+      <x:c r="E15" s="131" t="str">
+        <x:v>一致したホスト CI 
+cmdb_running_process
+cmdb_tcp
+cmdb_serial_number
+cmdb_rel_ci
+メトリック/イベント/ログ データ パイプライン</x:v>
+      </x:c>
+      <x:c r="F15" s="136" t="str">
+        <x:v>discovery_range_itemとデバイス履歴が一貫して含まれるのは、horizo​​ntal の IP 範囲スキャンのみです。他の機能には独自の範囲または入力があります。</x:v>
+      </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16" ht="87" customHeight="1">
+      <x:c r="A16" s="135" t="str">
+        <x:v>主な CMDB 出力</x:v>
+      </x:c>
+      <x:c r="B16" s="131" t="str">
+        <x:v>cmdb_ciおよび多数のサブクラス: サーバー、IP/NIC/DNS、CPU/メモリ/ディスク、ネットワーク デバイス、ストレージ、仮想化、アプリケーション、データベース、コンテナーなど。</x:v>
+      </x:c>
+      <x:c r="C16" s="131" t="str">
+        <x:v>クラウド リソースのサブクラス: データセンター/AZ、VM、テンプレート、セキュリティ グループ、VPC/ネットワーク/サブネット/NIC、ボリューム、LB、データベース、ストレージ アカウント、Kubernetes など。</x:v>
+      </x:c>
+      <x:c r="D16" s="131" t="str">
+        <x:v>cmdb_ci_service_discovered
+cmdb_ci_service_auto
+cmdb_ci_service_by_tags
+cmdb_ci_service_manual
+cmdb_ci_query_based_service
+および既存メンバー cmdb_ci_*</x:v>
+      </x:c>
+      <x:c r="E16" s="131" t="str">
+        <x:v>ホスト/サーバー CI、cmdb_running_process、cmdb_tcp、cmdb_serial_number、アプリケーション サブクラス。ファイル、証明書、監視、ログ機能にも独自の専用テーブルがあります。</x:v>
+      </x:c>
+      <x:c r="F16" s="136" t="str">
+        <x:v>Service Mappingの中核となる新しいオブジェクトはアプリケーション サービスです。そのメンバー CI のほとんどは他の検出ソースからのものです。</x:v>
+      </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17" ht="87" customHeight="1">
+      <x:c r="A17" s="135" t="str">
+        <x:v>共通して関係する主要テーブル</x:v>
+      </x:c>
+      <x:c r="B17" s="131" t="str">
+        <x:v>cmdb_ci
+cmdb_rel_ci
+sys_object_source
+cmdb_datasource_last_update
+IRE関連テーブル</x:v>
+      </x:c>
+      <x:c r="C17" s="131" t="str">
+        <x:v>cmdb_ci
+cmdb_rel_ci
+cmdb_key_value
+sys_object_source
+cmdb_datasource_last_update
+IRE関連テーブル</x:v>
+      </x:c>
+      <x:c r="D17" s="131" t="str">
+        <x:v>cmdb_ci
+cmdb_rel_ci
+svc_ci_assoc
+cmdb_running_process
+cmdb_tcp
+cmdb_key_value</x:v>
+      </x:c>
+      <x:c r="E17" s="131" t="str">
+        <x:v>cmdb_ci
+cmdb_rel_ci
+cmdb_running_process
+cmdb_tcp
+cmdb_serial_number</x:v>
+      </x:c>
+      <x:c r="F17" s="136" t="str">
+        <x:v>cmdb_ciと cmdb_rel_ciが主な交点です。 IRE/データ ソースの優先順位は、異なるソースからの CI 作成の重複を回避する役割を果たします。</x:v>
+      </x:c>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18" ht="64.5" customHeight="1">
+      <x:c r="A18" s="135" t="str">
+        <x:v>主なメリット</x:v>
+      </x:c>
+      <x:c r="B18" s="131" t="str">
+        <x:v>広範囲をカバーし、エージェントを必要としないため、ネットワーク機器、ストレージ、仮想化、従来のデータセンターに特に適しています。</x:v>
+      </x:c>
+      <x:c r="C18" s="131" t="str">
+        <x:v>IP ごとのスキャンを必要とせずに、幅広いクラウド リソースとタグを取得できるため、弾力性があり、ライフサイクルが短く、マルチアカウントの環境に適しています。</x:v>
+      </x:c>
+      <x:c r="D18" s="131" t="str">
+        <x:v>技術リソースをビジネスが理解できるサービス トポロジに変換して、影響分析、イベントの関連付け、変更リスクの判断をサポートします。</x:v>
+      </x:c>
+      <x:c r="E18" s="131" t="str">
+        <x:v>リモート エンドポイント、隔離ゾーン、動的 IP、および受信スキャン、ホスト内部データの継続的取得を許可しないデバイスに適しています。</x:v>
+      </x:c>
+      <x:c r="F18" s="136" t="str">
+        <x:v>選択は、「資産カバレッジ、クラウド コントロール プレーン、ホストの深さ、ビジネス トポロジ」の 4 つの目的とは別に検討する必要があります。</x:v>
+      </x:c>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19" ht="64.5" customHeight="1">
+      <x:c r="A19" s="135" t="str">
+        <x:v>主な制約</x:v>
+      </x:c>
+      <x:c r="B19" s="131" t="str">
+        <x:v>ネットワークの到達可能性、ポート、資格情報によって異なります。スキャン ウィンドウ、資格情報のロック、ネットワーク負荷を管理する必要があります。ビジネス サービスの境界が自動的に形成されるわけではありません。</x:v>
+      </x:c>
+      <x:c r="C19" s="131" t="str">
+        <x:v>クラウド API の認可スコープ内のデータのみが表示されます。通常、ホストの内部検出を置き換えることはできません。リソースのタイプはPattern/コンテンツのバージョンによって異なります。</x:v>
+      </x:c>
+      <x:c r="D19" s="131" t="str">
+        <x:v>基礎となる CMDB の品質、エントリ ポイント、および資格情報に大きく依存します。サービス境界が正しくないと、分析に影響を与えるエラーが発生する可能性があります。</x:v>
+      </x:c>
+      <x:c r="E19" s="131" t="str">
+        <x:v>インストール、アップグレード、証明書のローテーション、ポリシー管理、エージェントの健全性監視が必要です。すべてのネットワーク/ストレージ デバイスが展開に適しているわけではありません。</x:v>
+      </x:c>
+      <x:c r="F19" s="136" t="str">
+        <x:v>どちらを単独で使用しても盲点がある可能性があります。大企業は、組み合わせ、データ ソースの優先順位付け、重複排除戦略を設計する必要があります。</x:v>
+      </x:c>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20" ht="64.5" customHeight="1">
+      <x:c r="A20" s="135" t="str">
+        <x:v>推奨実行頻度</x:v>
+      </x:c>
+      <x:c r="B20" s="131" t="str">
+        <x:v>ネットワークのサイズと変更率に基づいて定期的に実行されます。ネットワーク全体の同時スキャンを避けるために、コア インフラストラクチャでは毎日またはバッチ スケジュールが一般的です。</x:v>
+      </x:c>
+      <x:c r="C20" s="131" t="str">
+        <x:v>クラウド リソースは急速に変化し、多くの場合、従来のインフラストラクチャよりも頻繁に変化します。イベントトリガーや定期的な完全キャリブレーションと組み合わせることができます。</x:v>
+      </x:c>
+      <x:c r="D20" s="131" t="str">
+        <x:v>ベース CI の更新後に実行/更新します。重要なビジネス サービスでは、エントリ ポイントとトポロジを継続的に検証する必要があります。</x:v>
+      </x:c>
+      <x:c r="E20" s="131" t="str">
+        <x:v>ポリシー/チェックによって制御される継続的または高頻度のレポート。エンドポイントの CPU、ネットワーク、データ保持のコストに注意してください。</x:v>
+      </x:c>
+      <x:c r="F20" s="136" t="str">
+        <x:v>頻度をずらして、主要なサービス マップを更新する前にクラウド/水平/ACC が更新されていることを確認する必要があります。</x:v>
+      </x:c>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21" ht="64.5" customHeight="1">
+      <x:c r="A21" s="135" t="str">
+        <x:v>適した利用シナリオ</x:v>
+      </x:c>
+      <x:c r="B21" s="131" t="str">
+        <x:v>従来のデータセンター、サーバーネットワークセグメント、ネットワーク機器、ストレージ、仮想化プラットフォームの資産インベントリを実現し、エージェントをインストールする必要はありません。</x:v>
+      </x:c>
+      <x:c r="C21" s="131" t="str">
+        <x:v>複数のアカウント、マルチリージョンのリソース インベントリ、タグ管理、AWS/Azure/GCP/IBM/VMware Cloud の急速に変化するリソース。</x:v>
+      </x:c>
+      <x:c r="D21" s="131" t="str">
+        <x:v>重要なビジネス システム、URL/VIP から Web/アプリ/DB までの依存関係グラフ、障害の影響分析、サービスの健全性および変更の評価。</x:v>
+      </x:c>
+      <x:c r="E21" s="131" t="str">
+        <x:v>従業員のエンドポイント、リモート/ブランチ、DMZ、動的 IP は、プロセス/TCP/メトリクス/ログを必要とする受信ポート、ホストを開くことができません。</x:v>
+      </x:c>
+      <x:c r="F21" s="136" t="str">
+        <x:v>シーンの組み合わせが優先されます。詳しくはページ下部の「シーン選びのヒント」をご覧ください。</x:v>
+      </x:c>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23" ht="22.5" customHeight="1">
+      <x:c r="A23" s="124" t="str">
+        <x:v>2. 主な書き込み先／関連テーブル一覧（機能別）</x:v>
+      </x:c>
+      <x:c r="B23" s="124"/>
+      <x:c r="C23" s="124"/>
+      <x:c r="D23" s="124"/>
+      <x:c r="E23" s="124"/>
+      <x:c r="F23" s="124"/>
+      <x:c r="G23" s="124"/>
+      <x:c r="H23" s="124"/>
+    </x:row>
+    <x:row r="24" ht="31.5" customHeight="1">
+      <x:c r="A24" s="130" t="str">
+        <x:v>大分類</x:v>
+      </x:c>
+      <x:c r="B24" s="130" t="str">
+        <x:v>テーブルグループ</x:v>
+      </x:c>
+      <x:c r="C24" s="130" t="str">
+        <x:v>主な物理テーブル</x:v>
+      </x:c>
+      <x:c r="D24" s="130" t="str">
+        <x:v>読み書きの性質</x:v>
+      </x:c>
+      <x:c r="E24" s="130" t="str">
+        <x:v>主な用途</x:v>
+      </x:c>
+      <x:c r="F24" s="130" t="str">
+        <x:v>固有／重複</x:v>
+      </x:c>
+      <x:c r="G24" s="130" t="str">
+        <x:v>相違点／注意事項</x:v>
+      </x:c>
+      <x:c r="H24" s="130" t="str">
+        <x:v>公式リファレンス</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="77.25" customHeight="1">
+      <x:c r="A25" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B25" s="131" t="str">
+        <x:v>範囲とスケジュール</x:v>
+      </x:c>
+      <x:c r="C25" s="131" t="str">
+        <x:v>discovery_schedule
+discovery_range_item
+discovery_range_item_ip
+ip_address_range
+ip_exclusion</x:v>
+      </x:c>
+      <x:c r="D25" s="131" t="str">
+        <x:v>主に読んでいます。スケジュールが実行されると更新される</x:v>
+      </x:c>
+      <x:c r="E25" s="131" t="str">
+        <x:v>IP 範囲、リスト、除外、および実行計画。</x:v>
+      </x:c>
+      <x:c r="F25" s="131" t="str">
+        <x:v>比較的固有</x:v>
+      </x:c>
+      <x:c r="G25" s="131" t="str">
+        <x:v>IP範囲の詳細な表については、「IP範囲表調査」を参照してください。</x:v>
+      </x:c>
+      <x:c r="H25" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/discovery/t_CreateADiscoverySchedule.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="77.25" customHeight="1">
+      <x:c r="A26" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B26" s="131" t="str">
+        <x:v>MID/認証情報/プロトコル</x:v>
+      </x:c>
+      <x:c r="C26" s="131" t="str">
+        <x:v>ecc_agent
+discovery_credentials
+dscy_credentials_affinity
+cmdb_ip_service
+discovery_port_probe</x:v>
+      </x:c>
+      <x:c r="D26" s="131" t="str">
+        <x:v>読み取り；アフィニティ条件の書き込み</x:v>
+      </x:c>
+      <x:c r="E26" s="131" t="str">
+        <x:v>MID、認証ターゲット、開いているポートに基づいたトリガー分類を選択します。</x:v>
+      </x:c>
+      <x:c r="F26" s="131" t="str">
+        <x:v>比較的固有</x:v>
+      </x:c>
+      <x:c r="G26" s="131" t="str">
+        <x:v>ACC は MID を通過することもできますが、エンドポイント スキャンに IP 範囲とポート プローブを使用しません。</x:v>
+      </x:c>
+      <x:c r="H26" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/discovery/c_GetStartedWithDiscovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="99.75" customHeight="1">
+      <x:c r="A27" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B27" s="131" t="str">
+        <x:v>分類と内容</x:v>
+      </x:c>
+      <x:c r="C27" s="131" t="str">
+        <x:v>discovery_probes
+discovery_sensor
+discovery_classy
+discovery_class_criteria
+discovery_classifier_probe
+discovery_classy_proc
+sa_pattern</x:v>
+      </x:c>
+      <x:c r="D27" s="131" t="str">
+        <x:v>読み取り</x:v>
+      </x:c>
+      <x:c r="E27" s="131" t="str">
+        <x:v>Shazzam のProbe／Sensor/Patternの定義、分類、識別、および探索。</x:v>
+      </x:c>
+      <x:c r="F27" s="131" t="str">
+        <x:v>比較的固有</x:v>
+      </x:c>
+      <x:c r="G27" s="131" t="str">
+        <x:v>最近のコンテンツはPatternが大半を占めていますが、スキャンと分類の段階は依然として存在します。</x:v>
+      </x:c>
+      <x:c r="H27" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/discovery/c_GetStartedWithDiscovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="99.75" customHeight="1">
+      <x:c r="A28" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B28" s="131" t="str">
+        <x:v>実行と診断</x:v>
+      </x:c>
+      <x:c r="C28" s="131" t="str">
+        <x:v>discovery_status
+discovery_device_history
+discovery_log
+ecc_queue
+ecc_queue_event
+shazzam_status
+shazzam_summary</x:v>
+      </x:c>
+      <x:c r="D28" s="131" t="str">
+        <x:v>書き込み/更新/回転</x:v>
+      </x:c>
+      <x:c r="E28" s="131" t="str">
+        <x:v>動作、デバイスレベルのステータス、ログ、MID メッセージ、およびスキャン統計。</x:v>
+      </x:c>
+      <x:c r="F28" s="131" t="str">
+        <x:v>一部共有</x:v>
+      </x:c>
+      <x:c r="G28" s="131" t="str">
+        <x:v>discovery_device_historyテーブルと Shazzam テーブルは、IP ベースの水平の特性を最もよく反映しています。</x:v>
+      </x:c>
+      <x:c r="H28" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/discovery/c_GetStartedWithDiscovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="88.5" customHeight="1">
+      <x:c r="A29" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B29" s="131" t="str">
+        <x:v>IRE/ソース管理</x:v>
+      </x:c>
+      <x:c r="C29" s="131" t="str">
+        <x:v>sys_object_source
+sys_rel_source
+cmdb_datasource_last_update
+cmdb_ire_partial_payloads
+cmdb_ire_partial_payloads_index
+cmdb_ire_incomplete_payloads</x:v>
+      </x:c>
+      <x:c r="D29" s="131" t="str">
+        <x:v>条件付き書き込み/クエリ</x:v>
+      </x:c>
+      <x:c r="E29" s="131" t="str">
+        <x:v>識別、重複排除、ソース追跡、調整、および異常なペイロード。</x:v>
+      </x:c>
+      <x:c r="F29" s="131" t="str">
+        <x:v>広く共有</x:v>
+      </x:c>
+      <x:c r="G29" s="131" t="str">
+        <x:v>Cloud Discovery と ACC は、CMDB に書き込むときに IRE/オリジン制御も通過する必要があります。</x:v>
+      </x:c>
+      <x:c r="H29" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/ire.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="111" customHeight="1">
+      <x:c r="A30" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B30" s="131" t="str">
+        <x:v>インフラストラクチャCI</x:v>
+      </x:c>
+      <x:c r="C30" s="131" t="str">
+        <x:v>cmdb_ci
+cmdb_ci_computer
+cmdb_ci_serverおよび OS サブクラス 
+cmdb_ci_ip_address
+cmdb_ci_network_adapter
+cmdb_ci_dns_name
+cmdb_serial_number
+cmdb_rel_ci</x:v>
+      </x:c>
+      <x:c r="D30" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E30" s="131" t="str">
+        <x:v>サーバー、アドレス、インターフェイス、名前、シリアル番号、および直接の関係。</x:v>
+      </x:c>
+      <x:c r="F30" s="131" t="str">
+        <x:v>ACC と重複</x:v>
+      </x:c>
+      <x:c r="G30" s="131" t="str">
+        <x:v>水平および ACC はホスト CI で重複する可能性があり、IRE および調整されたソースの優先順位付けに依存する必要があります。</x:v>
+      </x:c>
+      <x:c r="H30" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/discovery/c_GetStartedWithDiscovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="111" customHeight="1">
+      <x:c r="A31" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B31" s="131" t="str">
+        <x:v>コンポーネントとソフトウェア</x:v>
+      </x:c>
+      <x:c r="C31" s="131" t="str">
+        <x:v>cmdb_ci_cpu
+cmdb_ci_memory_module
+cmdb_ci_disk
+cmdb_ci_file_system
+cmdb_sam_sw_install
+cmdb_ci_spkg
+cmdb_running_process
+cmdb_tcp</x:v>
+      </x:c>
+      <x:c r="D31" s="131" t="str">
+        <x:v>条件付き挿入／更新／削除</x:v>
+      </x:c>
+      <x:c r="E31" s="131" t="str">
+        <x:v>ホストコンポーネント、ソフトウェア、プロセス、接続。</x:v>
+      </x:c>
+      <x:c r="F31" s="131" t="str">
+        <x:v>ACC と重複</x:v>
+      </x:c>
+      <x:c r="G31" s="131" t="str">
+        <x:v>収集は、OS、Pattern、SAM コンテンツ、スケジュール モードによって異なります。</x:v>
+      </x:c>
+      <x:c r="H31" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/itom-visibility/r_DataCollDiscoTCPConnections.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="88.5" customHeight="1">
+      <x:c r="A32" s="135" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B32" s="131" t="str">
+        <x:v>デバイスとプラットフォーム</x:v>
+      </x:c>
+      <x:c r="C32" s="131" t="str">
+        <x:v>cmdb_ci_netgearおよびネットワーク サブクラス 
+cmdb_ci_storage_*サブクラス 
+cmdb_ci_vcenter*/ vm_instance
+cmdb_ci_cluster*サブクラス 
+cmdb_ci_kubernetes*/ コンテナ サブクラス 
+cmdb_ci_appl/データベースサブクラス</x:v>
+      </x:c>
+      <x:c r="D32" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E32" s="131" t="str">
+        <x:v>ネットワーキング、ストレージ、仮想化、クラスター、コンテナー、アプリケーション、データベース。</x:v>
+      </x:c>
+      <x:c r="F32" s="131" t="str">
+        <x:v>最も広い範囲をカバー</x:v>
+      </x:c>
+      <x:c r="G32" s="131" t="str">
+        <x:v>ACCをインストールできないネットワークやストレージなどのデバイスは主にhorizo​​ntalに依存します。</x:v>
+      </x:c>
+      <x:c r="H32" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/discovery/c_GetStartedWithDiscovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="99.75" customHeight="1">
+      <x:c r="A33" s="141" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B33" s="131" t="str">
+        <x:v>協力リンク</x:v>
+      </x:c>
+      <x:c r="C33" s="131" t="str">
+        <x:v>discovery_schedule
+discovery_status
+discovery_log
+ecc_queue
+ecc_agent
+sys_object_source
+cmdb_datasource_last_update</x:v>
+      </x:c>
+      <x:c r="D33" s="131" t="str">
+        <x:v>読み取りと書き込みの実行</x:v>
+      </x:c>
+      <x:c r="E33" s="131" t="str">
+        <x:v>クラウド スケジュール、MID/API 呼び出し、ログ、ソース、最終更新時刻。</x:v>
+      </x:c>
+      <x:c r="F33" s="131" t="str">
+        <x:v>Horizontal Discovery と共有</x:v>
+      </x:c>
+      <x:c r="G33" s="131" t="str">
+        <x:v>クラウド アカウントの構成と API 権限オブジェクトは、プロバイダーとプラグインのバージョンによって異なります。</x:v>
+      </x:c>
+      <x:c r="H33" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/it-operations-management/discovery/cloud-discovery-wizard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="99.75" customHeight="1">
+      <x:c r="A34" s="141" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B34" s="131" t="str">
+        <x:v>クラウドの組織階層</x:v>
+      </x:c>
+      <x:c r="C34" s="131" t="str">
+        <x:v>cmdb_ci_cloud_service_account
+cmdb_ci_aws_datacenter
+cmdb_ci_ibm_datacenter
+cmdb_ci_availability_zone
+cmdb_ci_resource_group
+cmdb_ci_cloud_org
+cmdb_ci_cloud_space</x:v>
+      </x:c>
+      <x:c r="D34" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E34" s="131" t="str">
+        <x:v>アカウント、データセンター/リージョン/アリゾナ州、リソース グループ、組織、およびスペース。</x:v>
+      </x:c>
+      <x:c r="F34" s="131" t="str">
+        <x:v>クラウド固有</x:v>
+      </x:c>
+      <x:c r="G34" s="131" t="str">
+        <x:v>クラウドが異なれば、使用する層とプロバイダーのサブクラスも異なります。</x:v>
+      </x:c>
+      <x:c r="H34" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="88.5" customHeight="1">
+      <x:c r="A35" s="141" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B35" s="131" t="str">
+        <x:v>計算とテンプレート</x:v>
+      </x:c>
+      <x:c r="C35" s="131" t="str">
+        <x:v>cmdb_ci_vm_instance
+cmdb_ci_vmware_instance
+cmdb_ci_compute_template
+cmdb_ci_os_template
+cmdb_ci_hardware_type
+cmdb_ci_compute_security_group</x:v>
+      </x:c>
+      <x:c r="D35" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E35" s="131" t="str">
+        <x:v>VM、イメージ、仕様/テンプレート、セキュリティ グループ。</x:v>
+      </x:c>
+      <x:c r="F35" s="131" t="str">
+        <x:v>仮想化の検出と部分的に重複します</x:v>
+      </x:c>
+      <x:c r="G35" s="131" t="str">
+        <x:v>クラウド API はコントロール プレーン情報を取得します。 OS の内部属性には、依然として horizo​​ntal または ACC が必要です。</x:v>
+      </x:c>
+      <x:c r="H35" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="133.5" customHeight="1">
+      <x:c r="A36" s="141" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B36" s="131" t="str">
+        <x:v>クラウドネットワーク</x:v>
+      </x:c>
+      <x:c r="C36" s="131" t="str">
+        <x:v>cmdb_ci_network
+cmdb_ci_cloud_subnet
+cmdb_ci_nic
+cmdb_ci_cloud_public_ipaddress
+cmdb_ci_network_acl
+cmdb_ci_network_acl_rule
+cmdb_ci_cloud_load_balancer
+cmdb_ci_lb_service
+cmdb_ci_lb_pool
+cmdb_ci_lb_pool_member</x:v>
+      </x:c>
+      <x:c r="D36" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E36" s="131" t="str">
+        <x:v>VPC/VNet、サブネット、ネットワーク カード、パブリック IP、ACL、ファイアウォール、ロード バランシング。</x:v>
+      </x:c>
+      <x:c r="F36" s="131" t="str">
+        <x:v>主にクラウド固有</x:v>
+      </x:c>
+      <x:c r="G36" s="131" t="str">
+        <x:v>Service Mappingおよびクラウド サービスの影響分析の基礎として使用できます。</x:v>
+      </x:c>
+      <x:c r="H36" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="77.25" customHeight="1">
+      <x:c r="A37" s="141" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B37" s="131" t="str">
+        <x:v>ストレージ/データベース/ウェブ</x:v>
+      </x:c>
+      <x:c r="C37" s="131" t="str">
+        <x:v>cmdb_ci_storage_volume
+cmdb_ci_storage_vol_snapshot
+cmdb_ci_cloud_storage_account
+cmdb_ci_cloud_database
+cmdb_ci_cloud_webserver</x:v>
+      </x:c>
+      <x:c r="D37" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E37" s="131" t="str">
+        <x:v>クラウド ディスク、スナップショット、オブジェクト/ストレージ アカウント、管理されたデータベース、Web サービス。</x:v>
+      </x:c>
+      <x:c r="F37" s="131" t="str">
+        <x:v>クラウド固有</x:v>
+      </x:c>
+      <x:c r="G37" s="131" t="str">
+        <x:v>マネージド PaaS サービスは、完全な検出を行うために従来の IP スキャンに依存できません。</x:v>
+      </x:c>
+      <x:c r="H37" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="66" customHeight="1">
+      <x:c r="A38" s="141" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B38" s="131" t="str">
+        <x:v>容器とラベル</x:v>
+      </x:c>
+      <x:c r="C38" s="131" t="str">
+        <x:v>cmdb_ci_kubernetes_cluster
+cmdb_key_value
+cmdb_rel_ci</x:v>
+      </x:c>
+      <x:c r="D38" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E38" s="131" t="str">
+        <x:v>管理された Kubernetes クラスター、クラウド タグ、およびリソース関係。</x:v>
+      </x:c>
+      <x:c r="F38" s="131" t="str">
+        <x:v>Service Mapping と共有</x:v>
+      </x:c>
+      <x:c r="G38" s="131" t="str">
+        <x:v>タグベースのマッピングは、cmdb_key_valueとクラウド リソース CI を直接使用します。</x:v>
+      </x:c>
+      <x:c r="H38" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="66" customHeight="1">
+      <x:c r="A39" s="145" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B39" s="131" t="str">
+        <x:v>アプリケーションサービスの基本クラス</x:v>
+      </x:c>
+      <x:c r="C39" s="131" t="str">
+        <x:v>cmdb_ci_service_auto
+cmdb_ci_service_discovered</x:v>
+      </x:c>
+      <x:c r="D39" s="131" t="str">
+        <x:v>挿入/更新</x:v>
+      </x:c>
+      <x:c r="E39" s="131" t="str">
+        <x:v>自動/トップダウンマッピングによって生成されるアプリケーションサービス。</x:v>
+      </x:c>
+      <x:c r="F39" s="131" t="str">
+        <x:v>Service Mapping の中核</x:v>
+      </x:c>
+      <x:c r="G39" s="131" t="str">
+        <x:v>メンバーのテクニカル CI は通常、他の検出方法によって作成されています。</x:v>
+      </x:c>
+      <x:c r="H39" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/it-operations-management/itom-visibility/itom-visibility-use-case.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="66" customHeight="1">
+      <x:c r="A40" s="145" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B40" s="131" t="str">
+        <x:v>その他のサービス定義</x:v>
+      </x:c>
+      <x:c r="C40" s="131" t="str">
+        <x:v>cmdb_ci_service_by_tags
+cmdb_ci_service_manual
+cmdb_ci_query_based_service</x:v>
+      </x:c>
+      <x:c r="D40" s="131" t="str">
+        <x:v>挿入/更新または動的計算</x:v>
+      </x:c>
+      <x:c r="E40" s="131" t="str">
+        <x:v>タブ付き、手動、およびクエリベースのアプリケーション サービス。</x:v>
+      </x:c>
+      <x:c r="F40" s="131" t="str">
+        <x:v>Service Mapping/CMDB 独自のサービス モデリング</x:v>
+      </x:c>
+      <x:c r="G40" s="131" t="str">
+        <x:v>成熟度や自動化のレベルに応じて、さまざまなタイプが適しています。</x:v>
+      </x:c>
+      <x:c r="H40" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="66" customHeight="1">
+      <x:c r="A41" s="145" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B41" s="131" t="str">
+        <x:v>サービスメンバーと関係</x:v>
+      </x:c>
+      <x:c r="C41" s="131" t="str">
+        <x:v>svc_ci_assoc
+cmdb_rel_ci
+既存 cmdb_ci_*</x:v>
+      </x:c>
+      <x:c r="D41" s="131" t="str">
+        <x:v>挿入/更新/クエリ</x:v>
+      </x:c>
+      <x:c r="E41" s="131" t="str">
+        <x:v>メンバー CI へのサービス、およびメンバー間の技術的な依存関係。</x:v>
+      </x:c>
+      <x:c r="F41" s="131" t="str">
+        <x:v>サービスレイヤー固有</x:v>
+      </x:c>
+      <x:c r="G41" s="131" t="str">
+        <x:v>Service Mappingの価値は、すべての資産を再作成することではなく、メンバーと依存関係を整理することにあります。</x:v>
+      </x:c>
+      <x:c r="H41" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/service-mapping/service-mapping-get-started.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="66" customHeight="1">
+      <x:c r="A42" s="145" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B42" s="131" t="str">
+        <x:v>ランタイム通信入力</x:v>
+      </x:c>
+      <x:c r="C42" s="131" t="str">
+        <x:v>cmdb_running_process
+cmdb_tcp</x:v>
+      </x:c>
+      <x:c r="D42" s="131" t="str">
+        <x:v>関係を読み取り、場合によっては更新する</x:v>
+      </x:c>
+      <x:c r="E42" s="131" t="str">
+        <x:v>プロセス、リスニング ポート、および通信ピアは、依存関係を推測するために使用されます。</x:v>
+      </x:c>
+      <x:c r="F42" s="131" t="str">
+        <x:v>水平/ACCで共有</x:v>
+      </x:c>
+      <x:c r="G42" s="131" t="str">
+        <x:v>入力品質はマッピング結果に直接影響します。</x:v>
+      </x:c>
+      <x:c r="H42" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/itom-visibility/r_DataCollDiscoTCPConnections.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="66" customHeight="1">
+      <x:c r="A43" s="145" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B43" s="131" t="str">
+        <x:v>タグ入力</x:v>
+      </x:c>
+      <x:c r="C43" s="131" t="str">
+        <x:v>cmdb_key_value
+cmdb_ci_service_by_tags</x:v>
+      </x:c>
+      <x:c r="D43" s="131" t="str">
+        <x:v>読み取り/挿入/更新</x:v>
+      </x:c>
+      <x:c r="E43" s="131" t="str">
+        <x:v>Cloud Tag または Key-Value ルールによってサービスを構成します。</x:v>
+      </x:c>
+      <x:c r="F43" s="131" t="str">
+        <x:v>クラウドで共有</x:v>
+      </x:c>
+      <x:c r="G43" s="131" t="str">
+        <x:v>これは、成熟したタグ管理を備えたクラウド環境に適していますが、タグは実行時の依存関係を完全には表現できません。</x:v>
+      </x:c>
+      <x:c r="H43" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/it-operations-management/itom-visibility/itom-visibility-use-case.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="66" customHeight="1">
+      <x:c r="A44" s="145" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B44" s="131" t="str">
+        <x:v>基礎となるオペレーティングリンク</x:v>
+      </x:c>
+      <x:c r="C44" s="131" t="str">
+        <x:v>ecc_queue、Discovery/MID のログおよびPattern関連レコード</x:v>
+      </x:c>
+      <x:c r="D44" s="131" t="str">
+        <x:v>読み取りと条件付き書き込み</x:v>
+      </x:c>
+      <x:c r="E44" s="131" t="str">
+        <x:v>Discovery/MID 経由でポータルとテクノロジー スタックにアクセスします。</x:v>
+      </x:c>
+      <x:c r="F44" s="131" t="str">
+        <x:v>上流機能に依存</x:v>
+      </x:c>
+      <x:c r="G44" s="131" t="str">
+        <x:v>公式に明らかにされているのは、Service Mappingはディスカバリーに依存しているということです。独立した資産インベントリ ツールとして使用することはできません。</x:v>
+      </x:c>
+      <x:c r="H44" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/service-mapping/service-mapping-get-started.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="66" customHeight="1">
+      <x:c r="A45" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B45" s="131" t="str">
+        <x:v>基本的なホスト CI</x:v>
+      </x:c>
+      <x:c r="C45" s="131" t="str">
+        <x:v>cmdb_ci_computer
+cmdb_ci_serverおよび OS サブクラス</x:v>
+      </x:c>
+      <x:c r="D45" s="131" t="str">
+        <x:v>マッチング後に挿入/更新</x:v>
+      </x:c>
+      <x:c r="E45" s="131" t="str">
+        <x:v>名前、OS、CPU、メモリ、IP、ゲートウェイ、シリアル番号、FQDN。</x:v>
+      </x:c>
+      <x:c r="F45" s="131" t="str">
+        <x:v>水平方向と重なる</x:v>
+      </x:c>
+      <x:c r="G45" s="131" t="str">
+        <x:v>ホスト テーブルは IRE の照合結果によって決定されるため、エージェントに対して別の CI を作成しないでください。</x:v>
+      </x:c>
+      <x:c r="H45" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/acc-data-collection.html?contentId=XF2OUrZDVSv4nM40Vq66bg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="66" customHeight="1">
+      <x:c r="A46" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B46" s="131" t="str">
+        <x:v>プロセス/接続/シリアル番号</x:v>
+      </x:c>
+      <x:c r="C46" s="131" t="str">
+        <x:v>cmdb_running_process
+cmdb_tcp
+cmdb_serial_number
+cmdb_rel_ci</x:v>
+      </x:c>
+      <x:c r="D46" s="131" t="str">
+        <x:v>挿入/更新</x:v>
+      </x:c>
+      <x:c r="E46" s="131" t="str">
+        <x:v>ホストの内部プロセス、TCP、シーケンス番号、および関係。</x:v>
+      </x:c>
+      <x:c r="F46" s="131" t="str">
+        <x:v>水平/サービスマッピングと共有</x:v>
+      </x:c>
+      <x:c r="G46" s="131" t="str">
+        <x:v>より継続的なホスト稼働データをService Mappingに提供できます。</x:v>
+      </x:c>
+      <x:c r="H46" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/acc-data-collection.html?contentId=XF2OUrZDVSv4nM40Vq66bg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="66" customHeight="1">
+      <x:c r="A47" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B47" s="131" t="str">
+        <x:v>Patternの適用</x:v>
+      </x:c>
+      <x:c r="C47" s="131" t="str">
+        <x:v>cmdb_ci_applおよび製品サブクラス 
+データベース/ミドルウェア/Web サーバーは cmdb_ci_*に対応します</x:v>
+      </x:c>
+      <x:c r="D47" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E47" s="131" t="str">
+        <x:v>ACC-VC チェック/Patternによって識別されるアプリケーションとコンポーネント。</x:v>
+      </x:c>
+      <x:c r="F47" s="131" t="str">
+        <x:v>水平方向と重なる</x:v>
+      </x:c>
+      <x:c r="G47" s="131" t="str">
+        <x:v>実際のテーブル名は、ACC-VC コンテンツ パックとPatternによって異なります。</x:v>
+      </x:c>
+      <x:c r="H47" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/yokohama/it-operations-management/agent-client-collector/acc-visibility-landing-page.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="88.5" customHeight="1">
+      <x:c r="A48" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B48" s="131" t="str">
+        <x:v>Java ファイルの検出</x:v>
+      </x:c>
+      <x:c r="C48" s="131" t="str">
+        <x:v>ora_java_audit
+ora_java_evidence / cmdb_ora_java_evidence
+cmdb_sam_sw_install
+cmdb_file_information
+cmdb_ci_appl
+cmdb_ci_computer</x:v>
+      </x:c>
+      <x:c r="D48" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E48" s="131" t="str">
+        <x:v>Java のインストール、ドキュメント、ソフトウェアの証拠およびリファレンス。</x:v>
+      </x:c>
+      <x:c r="F48" s="131" t="str">
+        <x:v>ACC拡張専用</x:v>
+      </x:c>
+      <x:c r="G48" s="131" t="str">
+        <x:v>Java 資産/ライセンスの証明を必要とするエンドポイントに適しています。</x:v>
+      </x:c>
+      <x:c r="H48" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/acc-data-collection.html?contentId=XF2OUrZDVSv4nM40Vq66bg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="66" customHeight="1">
+      <x:c r="A49" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B49" s="131" t="str">
+        <x:v>証明書の検出</x:v>
+      </x:c>
+      <x:c r="C49" s="131" t="str">
+        <x:v>cmdb_ci_certificate
+sn_disco_certmgmt_certificate_history
+sn_disco_certmgmt_cmdb_installed_certificate</x:v>
+      </x:c>
+      <x:c r="D49" s="131" t="str">
+        <x:v>条件付き挿入／更新</x:v>
+      </x:c>
+      <x:c r="E49" s="131" t="str">
+        <x:v>エンドポイント証明書、履歴、インストール関係。</x:v>
+      </x:c>
+      <x:c r="F49" s="131" t="str">
+        <x:v>IP ベースの証明書検出と重複します</x:v>
+      </x:c>
+      <x:c r="G49" s="131" t="str">
+        <x:v>証明書の検出ソースと頻度は調整する必要があります。</x:v>
+      </x:c>
+      <x:c r="H49" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/yokohama/it-operations-management/agent-client-collector/acc-visibility-landing-page.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="66" customHeight="1">
+      <x:c r="A50" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B50" s="131" t="str">
+        <x:v>Monitoring</x:v>
+      </x:c>
+      <x:c r="C50" s="131" t="str">
+        <x:v>メトリック ストア / メトリック インテリジェンス 
+em_event
+em_alert
+既存の cmdb_ci_*関連付け</x:v>
+      </x:c>
+      <x:c r="D50" s="131" t="str">
+        <x:v>インジケーターを継続的に書き込みます。ルール条件によりイベント/アラームが生成される</x:v>
+      </x:c>
+      <x:c r="E50" s="131" t="str">
+        <x:v>CPU、メモリ、ディスク、プロセス、アプリケーション、URL、クラウドのメトリクス。</x:v>
+      </x:c>
+      <x:c r="F50" s="131" t="str">
+        <x:v>ACC-M専用</x:v>
+      </x:c>
+      <x:c r="G50" s="131" t="str">
+        <x:v>モニタリング データは CMDB 資産ではありません。 Discovery アセット テーブルと混同しないでください。</x:v>
+      </x:c>
+      <x:c r="H50" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/agent-client-collector/acc-landing-page.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="66" customHeight="1">
+      <x:c r="A51" s="149" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B51" s="131" t="str">
+        <x:v>Log Analytics</x:v>
+      </x:c>
+      <x:c r="C51" s="131" t="str">
+        <x:v>Health Log Analytics ログ ストレージ/インデックス 
+ACC データ入力/ストリーミング ソース レコード 
+既存の cmdb_ci_*アソシエーション</x:v>
+      </x:c>
+      <x:c r="D51" s="131" t="str">
+        <x:v>連続ストリーミング書き込み</x:v>
+      </x:c>
+      <x:c r="E51" s="131" t="str">
+        <x:v>Linux/Windows/アプリケーションのログと CI コンテキスト。</x:v>
+      </x:c>
+      <x:c r="F51" s="131" t="str">
+        <x:v>ACC-L専用</x:v>
+      </x:c>
+      <x:c r="G51" s="131" t="str">
+        <x:v>ログは、通常の cmdb_ci_*テーブルではなく、HLA データ パイプラインに入ります。</x:v>
+      </x:c>
+      <x:c r="H51" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/agent-client-collector/acc-landing-page.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52"/>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
+    </x:row>
+    <x:row r="53" ht="22.5" customHeight="1">
+      <x:c r="A53" s="124" t="str">
+        <x:v>3. シナリオ別選定指針</x:v>
+      </x:c>
+      <x:c r="B53" s="124"/>
+      <x:c r="C53" s="124"/>
+      <x:c r="D53" s="124"/>
+      <x:c r="E53" s="124"/>
+      <x:c r="F53"/>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+    </x:row>
+    <x:row r="54" ht="31.5" customHeight="1">
+      <x:c r="A54" s="130" t="str">
+        <x:v>想定シナリオ</x:v>
+      </x:c>
+      <x:c r="B54" s="130" t="str">
+        <x:v>推奨方式</x:v>
+      </x:c>
+      <x:c r="C54" s="130" t="str">
+        <x:v>補完方式</x:v>
+      </x:c>
+      <x:c r="D54" s="130" t="str">
+        <x:v>選定理由</x:v>
+      </x:c>
+      <x:c r="E54" s="130" t="str">
+        <x:v>導入・運用上の注意</x:v>
+      </x:c>
+      <x:c r="F54"/>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
+    </x:row>
+    <x:row r="55" ht="56.25" customHeight="1">
+      <x:c r="A55" s="135" t="str">
+        <x:v>従来のデータセンターのネットワーク全体にわたる資産のインベントリ</x:v>
+      </x:c>
+      <x:c r="B55" s="131" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="C55" s="131" t="str">
+        <x:v>サービスマッピング (重要なビジネス)</x:v>
+      </x:c>
+      <x:c r="D55" s="131" t="str">
+        <x:v>エージェントをインストールする必要がなく、サーバー、ネットワーク、ストレージ、仮想化を最も完全にカバーします。</x:v>
+      </x:c>
+      <x:c r="E55" s="131" t="str">
+        <x:v>ネットワークセグメントに応じてバッチで実行し、ピークをずらして実行します。まず、資格情報と MID カバレッジを改善します。</x:v>
+      </x:c>
+      <x:c r="F55"/>
+      <x:c r="G55"/>
+      <x:c r="H55"/>
+    </x:row>
+    <x:row r="56" ht="56.25" customHeight="1">
+      <x:c r="A56" s="135" t="str">
+        <x:v>AWS/Azure/GCP マルチアカウントのリソース インベントリ</x:v>
+      </x:c>
+      <x:c r="B56" s="131" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="C56" s="131" t="str">
+        <x:v>ACCまたは水平。サービスマッピング</x:v>
+      </x:c>
+      <x:c r="D56" s="131" t="str">
+        <x:v>クラウド API は、固定 IP に依存せずに、アカウント、リージョン、ホスティング サービス、ネットワーク、タグをカバーできます。</x:v>
+      </x:c>
+      <x:c r="E56" s="131" t="str">
+        <x:v>まず、IAM の最小権限とPattern バージョンを確認してから、VM 内部データを追加します。</x:v>
+      </x:c>
+      <x:c r="F56"/>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
+    </x:row>
+    <x:row r="57" ht="56.25" customHeight="1">
+      <x:c r="A57" s="135" t="str">
+        <x:v>クラウド VM の完全な資産と OS の深さ</x:v>
+      </x:c>
+      <x:c r="B57" s="131" t="str">
+        <x:v>Cloud Discovery + ACC</x:v>
+      </x:c>
+      <x:c r="C57" s="131" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="D57" s="131" t="str">
+        <x:v>クラウドはコントロール プレーンを提供し、ACC はホスト内部を提供します。どちらも IRE 経由で同じ CI をマージします。</x:v>
+      </x:c>
+      <x:c r="E57" s="131" t="str">
+        <x:v>データ ソースの優先順位を定義して、VM/サーバーの重複を回避します。</x:v>
+      </x:c>
+      <x:c r="F57"/>
+      <x:c r="G57"/>
+      <x:c r="H57"/>
+    </x:row>
+    <x:row r="58" ht="56.25" customHeight="1">
+      <x:c r="A58" s="135" t="str">
+        <x:v>主要なビジネス URL/VIP からデータベースへの依存関係グラフ</x:v>
+      </x:c>
+      <x:c r="B58" s="131" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="C58" s="131" t="str">
+        <x:v>水平/クラウド/ACC は基本的な CI を提供します</x:v>
+      </x:c>
+      <x:c r="D58" s="131" t="str">
+        <x:v>アセット マニフェストだけでなく、アプリケーション サービス、メンバーシップ、およびランタイムの依存関係が必要です。</x:v>
+      </x:c>
+      <x:c r="E58" s="131" t="str">
+        <x:v>まず、基本 CMDB 品質とエントリ資格情報を満たしている必要があります。</x:v>
+      </x:c>
+      <x:c r="F58"/>
+      <x:c r="G58"/>
+      <x:c r="H58"/>
+    </x:row>
+    <x:row r="59" ht="56.25" customHeight="1">
+      <x:c r="A59" s="135" t="str">
+        <x:v>ネットワーク機器、SAN、ストレージアレイ、PDU/UPS</x:v>
+      </x:c>
+      <x:c r="B59" s="131" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="C59" s="131" t="str">
+        <x:v>Service Mapping (サービス チェーンへの参加など)</x:v>
+      </x:c>
+      <x:c r="D59" s="131" t="str">
+        <x:v>これらのデバイスは通常、ACC ではインストールできず、主に SNMP/SSH/API 経由で検出されます。</x:v>
+      </x:c>
+      <x:c r="E59" s="131" t="str">
+        <x:v>スキャン頻度、SNMP 権限、デバイスの負荷を制御します。</x:v>
+      </x:c>
+      <x:c r="F59"/>
+      <x:c r="G59"/>
+      <x:c r="H59"/>
+    </x:row>
+    <x:row r="60" ht="56.25" customHeight="1">
+      <x:c r="A60" s="135" t="str">
+        <x:v>リモート オフィス、ブランチ、動的 IP、NAT バックエンドポイント</x:v>
+      </x:c>
+      <x:c r="B60" s="131" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="C60" s="131" t="str">
+        <x:v>到達可能なネットワーク資産の水平方向</x:v>
+      </x:c>
+      <x:c r="D60" s="131" t="str">
+        <x:v>エンドポイントはアクティブに接続するため、受信ポートとネットワークの到達可能性の要件が軽減されます。</x:v>
+      </x:c>
+      <x:c r="E60" s="131" t="str">
+        <x:v>エージェントのアップグレード、証明書のローテーション、健全性およびポリシーのガバナンスを確立します。</x:v>
+      </x:c>
+      <x:c r="F60"/>
+      <x:c r="G60"/>
+      <x:c r="H60"/>
+    </x:row>
+    <x:row r="61" ht="56.25" customHeight="1">
+      <x:c r="A61" s="135" t="str">
+        <x:v>DMZ/高セキュリティ ゾーンにより、MID によるアクティブなログインが禁止されます</x:v>
+      </x:c>
+      <x:c r="B61" s="131" t="str">
+        <x:v>ACC (エンドポイントが送信を許可されている場合)</x:v>
+      </x:c>
+      <x:c r="C61" s="131" t="str">
+        <x:v>隔離固有の MID + 水平</x:v>
+      </x:c>
+      <x:c r="D61" s="131" t="str">
+        <x:v>プッシュ モードは、厳格な受信制限に適しています。エージェントが無効になっている場合は、パーティション MID を使用します。</x:v>
+      </x:c>
+      <x:c r="E61" s="131" t="str">
+        <x:v>送信パスと証明書の信頼性はセキュリティ チームによって確認される必要があります。</x:v>
+      </x:c>
+      <x:c r="F61"/>
+      <x:c r="G61"/>
+      <x:c r="H61"/>
+    </x:row>
+    <x:row r="62" ht="56.25" customHeight="1">
+      <x:c r="A62" s="135" t="str">
+        <x:v>CPU/メモリ/プロセス/URLの継続的な監視</x:v>
+      </x:c>
+      <x:c r="B62" s="131" t="str">
+        <x:v>ACC Monitoring</x:v>
+      </x:c>
+      <x:c r="C62" s="131" t="str">
+        <x:v>Event Management / Metric Intelligence</x:v>
+      </x:c>
+      <x:c r="D62" s="131" t="str">
+        <x:v>水平/クラウドは資産検出用であり、継続的なメトリック収集には適していません。</x:v>
+      </x:c>
+      <x:c r="E62" s="131" t="str">
+        <x:v>監視頻度、しきい値、イベント ルール、およびデータ保持は個別に設計する必要があります。</x:v>
+      </x:c>
+      <x:c r="F62"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+    </x:row>
+    <x:row r="63" ht="56.25" customHeight="1">
+      <x:c r="A63" s="135" t="str">
+        <x:v>エンドポイントログの一元的な分析</x:v>
+      </x:c>
+      <x:c r="B63" s="131" t="str">
+        <x:v>ACC Log Analytics</x:v>
+      </x:c>
+      <x:c r="C63" s="131" t="str">
+        <x:v>既存のディスカバリー/ACC CI</x:v>
+      </x:c>
+      <x:c r="D63" s="131" t="str">
+        <x:v>ログ ストリームは HLA に入り、CMDB アセット スキャンではなく CI に関連付けられます。</x:v>
+      </x:c>
+      <x:c r="E63" s="131" t="str">
+        <x:v>ログの範囲、保存期間、機密情報、帯域幅を計画します。</x:v>
+      </x:c>
+      <x:c r="F63"/>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+    </x:row>
+    <x:row r="64" ht="56.25" customHeight="1">
+      <x:c r="A64" s="135" t="str">
+        <x:v>証明書の目録</x:v>
+      </x:c>
+      <x:c r="B64" s="131" t="str">
+        <x:v>ACC-VC 証明書検出 (エージェントがインストールされている)</x:v>
+      </x:c>
+      <x:c r="C64" s="131" t="str">
+        <x:v>IP ベースの証明書検出 (エージェントなし)</x:v>
+      </x:c>
+      <x:c r="D64" s="131" t="str">
+        <x:v>どちらのパスも証明書関連テーブルの書き込みに使用できますが、どちらのパスを選択するかは、エンドポイントのカバレッジとネットワークの到達可能性に依存します。</x:v>
+      </x:c>
+      <x:c r="E64" s="131" t="str">
+        <x:v>コレクションの重複を避けるためにソースとスケジュールを調整します。</x:v>
+      </x:c>
+      <x:c r="F64"/>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+    </x:row>
+    <x:row r="65" ht="56.25" customHeight="1">
+      <x:c r="A65" s="135" t="str">
+        <x:v>大規模ハイブリッド企業の推奨ベースライン</x:v>
+      </x:c>
+      <x:c r="B65" s="131" t="str">
+        <x:v>4方式の組み合わせ</x:v>
+      </x:c>
+      <x:c r="C65" s="131" t="str">
+        <x:v>サービスグラフコネクタとその他のソース</x:v>
+      </x:c>
+      <x:c r="D65" s="131" t="str">
+        <x:v>水平はローカル インフラストラクチャを管理し、クラウドはクラウド コントロール プレーンを管理し、ACC はエンドポイントの内部とテレメトリを管理し、Service Mappingはビジネスの依存関係を管理します。</x:v>
+      </x:c>
+      <x:c r="E65" s="131" t="str">
+        <x:v>IRE、調整、ソースの優先順位付け、命名規則、除外範囲、および実行カレンダーを統合します。</x:v>
+      </x:c>
+      <x:c r="F65"/>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+    </x:row>
+    <x:row r="67" ht="39" customHeight="1">
+      <x:c r="A67" s="117" t="str">
+        <x:v>最終推奨：大規模なハイブリッド企業では、Horizontal Discovery、Cloud Discovery、選択的な ACC を併用し、IRE／Reconciliation によって同一の信頼できる CI に統合することを推奨します。Service Mapping は業務影響分析が必要な重要システムを対象とし、ガバナンスされた CMDB を基盤として構築してください。</x:v>
+      </x:c>
+      <x:c r="B67" s="117"/>
+      <x:c r="C67" s="117"/>
+      <x:c r="D67" s="117"/>
+      <x:c r="E67" s="117"/>
+      <x:c r="F67" s="117"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A3:F3"/>
+    <x:mergeCell ref="A5:F5"/>
+    <x:mergeCell ref="A23:H23"/>
+    <x:mergeCell ref="A53:E53"/>
+    <x:mergeCell ref="A67:F67"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b56b60d59da474c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a59e58d78454e49"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44.380001068115234" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="43.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="43.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="48.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="A1" s="153" t="str">
+        <x:v>Discovery_ACC データ一覧：中分類の分類基準と利用方法</x:v>
+      </x:c>
+      <x:c r="B1" s="153"/>
+      <x:c r="C1" s="153"/>
+      <x:c r="D1" s="153"/>
+      <x:c r="E1" s="153"/>
+      <x:c r="F1" s="153"/>
+      <x:c r="G1" s="153"/>
+      <x:c r="H1" s="153"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="157" t="str">
+        <x:v>重要な結論：「中分類」は ServiceNow が提供する統一的な製品分類ツリーではありません。収集範囲、関連テーブル、適用シナリオを追跡しやすくするため、公式機能の境界に基づいて整理した調査用の分類です。</x:v>
+      </x:c>
+      <x:c r="B2" s="157"/>
+      <x:c r="C2" s="157"/>
+      <x:c r="D2" s="157"/>
+      <x:c r="E2" s="157"/>
+      <x:c r="F2" s="157"/>
+      <x:c r="G2" s="157"/>
+      <x:c r="H2" s="157"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="161" t="str">
+        <x:v>分類方針：ServiceNow 公式ページの製品名、機能名、Application Service タイプ、Data collected の対象領域を優先します。公式に統一階層がない場合は、収集起点、対象オブジェクト、クラウドプラットフォーム、データ用途で整理しています。作成日：2026-06-11。</x:v>
+      </x:c>
+      <x:c r="B3" s="161"/>
+      <x:c r="C3" s="161"/>
+      <x:c r="D3" s="161"/>
+      <x:c r="E3" s="161"/>
+      <x:c r="F3" s="161"/>
+      <x:c r="G3" s="161"/>
+      <x:c r="H3" s="161"/>
+    </x:row>
+    <x:row r="5" ht="22.5" customHeight="1">
+      <x:c r="A5" s="164" t="str">
+        <x:v>1. 大分類ごとの中分類の基準</x:v>
+      </x:c>
+      <x:c r="B5" s="164"/>
+      <x:c r="C5" s="164"/>
+      <x:c r="D5" s="164"/>
+      <x:c r="E5" s="164"/>
+      <x:c r="F5" s="164"/>
+      <x:c r="G5" s="164"/>
+      <x:c r="H5" s="164"/>
+    </x:row>
+    <x:row r="6" ht="31.5" customHeight="1">
+      <x:c r="A6" s="170" t="str">
+        <x:v>大分類</x:v>
+      </x:c>
+      <x:c r="B6" s="170" t="str">
+        <x:v>中分類の主な軸</x:v>
+      </x:c>
+      <x:c r="C6" s="170" t="str">
+        <x:v>この軸を採用する理由</x:v>
+      </x:c>
+      <x:c r="D6" s="170" t="str">
+        <x:v>本資料の中分類</x:v>
+      </x:c>
+      <x:c r="E6" s="170" t="str">
+        <x:v>公式性の考え方</x:v>
+      </x:c>
+      <x:c r="F6" s="170" t="str">
+        <x:v>主な公式根拠</x:v>
+      </x:c>
+      <x:c r="G6" s="170" t="str">
+        <x:v>解釈上の注意</x:v>
+      </x:c>
+      <x:c r="H6" s="170" t="str">
+        <x:v>官方 URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="156" customHeight="1">
+      <x:c r="A7" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B7" s="131" t="str">
+        <x:v>収集起点 + 検出対象となる技術オブジェクト領域</x:v>
+      </x:c>
+      <x:c r="C7" s="131" t="str">
+        <x:v>Horizontal Discovery は IP／ホストを起点にスキャンしますが、最終的な書き込み先は、識別されたサーバー、ネットワーク、ストレージ、アプリケーションなどの種類で決まります。</x:v>
+      </x:c>
+      <x:c r="D7" s="131" t="str">
+        <x:v>IP Range Discovery
+Operating System / Server
+Host Components
+Process &amp; TCP
+Software Discovery
+Application Discovery
+Database Discovery
+Network Discovery
+Storage Discovery
+Virtualization Discovery
+Clustered Applications
+Container Discovery</x:v>
+      </x:c>
+      <x:c r="E7" s="131" t="str">
+        <x:v>対象領域は主に公式の Data collected ページに基づきますが、「中分類」という階層自体は本資料で整理したものです。</x:v>
+      </x:c>
+      <x:c r="F7" s="131" t="str">
+        <x:v>Data collected by ITOM Visibility</x:v>
+      </x:c>
+      <x:c r="G7" s="131" t="str">
+        <x:v>IP Range は Discovery の起点であり CI タイプではありません。他の項目は主に対象オブジェクト領域であり、完全に同一階層ではありません。</x:v>
+      </x:c>
+      <x:c r="H7" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-by-itom-visibility.html?content-lang=en-US</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="99.75" customHeight="1">
+      <x:c r="A8" s="178" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B8" s="131" t="str">
+        <x:v>クラウドプロバイダー／クラウド管理プラットフォーム</x:v>
+      </x:c>
+      <x:c r="C8" s="131" t="str">
+        <x:v>公式ドキュメントでは AWS、Azure、GCP、IBM Cloud、VMware ごとに収集対象とテーブルが説明されています。API、リソース階層、クラスモデルも異なります。</x:v>
+      </x:c>
+      <x:c r="D8" s="131" t="str">
+        <x:v>AWS Discovery
+Microsoft Azure Discovery
+Google Cloud Platform Discovery
+IBM Cloud Discovery
+VMware Cloud / vCenter Discovery</x:v>
+      </x:c>
+      <x:c r="E8" s="131" t="str">
+        <x:v>基本的に公式ドキュメントのプロバイダー別分類を踏襲しています。</x:v>
+      </x:c>
+      <x:c r="F8" s="131" t="str">
+        <x:v>Cloud Discovery collected data</x:v>
+      </x:c>
+      <x:c r="G8" s="131" t="str">
+        <x:v>クラウドプロバイダーを中分類とし、Compute、Network、Storage などのリソース種別は小分類およびデータ／テーブル列で展開します。</x:v>
+      </x:c>
+      <x:c r="H8" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="88.5" customHeight="1">
+      <x:c r="A9" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B9" s="131" t="str">
+        <x:v>Application Service の作成方法／依存関係の根拠</x:v>
+      </x:c>
+      <x:c r="C9" s="131" t="str">
+        <x:v>Service Mapping の中心は資産の再棚卸しではなく、Entry Point、通信、タグ、クエリ、手動選択を利用してサービス境界とメンバー関係を構成することです。</x:v>
+      </x:c>
+      <x:c r="D9" s="131" t="str">
+        <x:v>Top-down Mapping
+Traffic-based Mapping
+Tag-based Mapping
+CMDB-based / Manual
+Automated Service Suggestions
+Dynamic CI Group</x:v>
+      </x:c>
+      <x:c r="E9" s="131" t="str">
+        <x:v>一部は公式の Application Service タイプ、一部は公式のマッピング／入力方式です。本資料では比較しやすいよう同じ調査階層に配置しています。</x:v>
+      </x:c>
+      <x:c r="F9" s="131" t="str">
+        <x:v>Service Mapping / Application Services</x:v>
+      </x:c>
+      <x:c r="G9" s="131" t="str">
+        <x:v>製品メニュー上で同一階層とは限らず、同じプラグインやライセンスで提供されることも意味しません。</x:v>
+      </x:c>
+      <x:c r="H9" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="88.5" customHeight="1">
+      <x:c r="A10" s="186" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B10" s="131" t="str">
+        <x:v>ACC コンポーネント + データ用途</x:v>
+      </x:c>
+      <x:c r="C10" s="131" t="str">
+        <x:v>ACC Framework、Visibility、Monitoring、Log Analytics は、収集目的、データパイプライン、対象テーブルが異なります。コンポーネント別に分けることで資産、メトリクス、ログの混同を防げます。</x:v>
+      </x:c>
+      <x:c r="D10" s="131" t="str">
+        <x:v>ACC Framework（ACC-F）
+ACC Visibility Content（ACC-VC）
+ACC Monitoring（ACC-M）
+ACC Log Analytics（ACC-L）</x:v>
+      </x:c>
+      <x:c r="E10" s="131" t="str">
+        <x:v>主に公式のコンポーネント／コンテンツ名を使用し、略称は資料の可読性のために付記しています。</x:v>
+      </x:c>
+      <x:c r="F10" s="131" t="str">
+        <x:v>Agent Client Collector</x:v>
+      </x:c>
+      <x:c r="G10" s="131" t="str">
+        <x:v>ACC-M のメトリクスと ACC-L のログは、通常の cmdb_ci_* 資産テーブルではありません。ACC-VC の資産 Discovery と同一視しないでください。</x:v>
+      </x:c>
+      <x:c r="H10" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/xanadu/it-operations-management/agent-client-collector/acc-landing-page.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="22.5" customHeight="1">
+      <x:c r="A12" s="164" t="str">
+        <x:v>2. 各中分類の判断基準</x:v>
+      </x:c>
+      <x:c r="B12" s="164"/>
+      <x:c r="C12" s="164"/>
+      <x:c r="D12" s="164"/>
+      <x:c r="E12" s="164"/>
+      <x:c r="F12" s="164"/>
+      <x:c r="G12" s="164"/>
+    </x:row>
+    <x:row r="13" ht="31.5" customHeight="1">
+      <x:c r="A13" s="170" t="str">
+        <x:v>大分類</x:v>
+      </x:c>
+      <x:c r="B13" s="170" t="str">
+        <x:v>中分類</x:v>
+      </x:c>
+      <x:c r="C13" s="170" t="str">
+        <x:v>分類基準／対象</x:v>
+      </x:c>
+      <x:c r="D13" s="170" t="str">
+        <x:v>公式上の位置付け</x:v>
+      </x:c>
+      <x:c r="E13" s="170" t="str">
+        <x:v>本資料での用途</x:v>
+      </x:c>
+      <x:c r="F13" s="170" t="str">
+        <x:v>解釈上の注意</x:v>
+      </x:c>
+      <x:c r="G13" s="170" t="str">
+        <x:v>公式リファレンス</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="66" customHeight="1">
+      <x:c r="A14" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B14" s="131" t="str">
+        <x:v>IP Range Discovery</x:v>
+      </x:c>
+      <x:c r="C14" s="131" t="str">
+        <x:v>収集起点と対象範囲</x:v>
+      </x:c>
+      <x:c r="D14" s="131" t="str">
+        <x:v>Discovery Schedule、IP Range、Shazzam、分類、Pattern の実行起点。</x:v>
+      </x:c>
+      <x:c r="E14" s="131" t="str">
+        <x:v>スキャン実行テーブルと、最終 CI テーブルが固定されない理由を説明します。</x:v>
+      </x:c>
+      <x:c r="F14" s="131" t="str">
+        <x:v>CI タイプではなく、Server や Network などの対象分類と完全な同一階層ではありません。</x:v>
+      </x:c>
+      <x:c r="G14" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-by-itom-visibility.html?content-lang=en-US</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="66" customHeight="1">
+      <x:c r="A15" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B15" s="131" t="str">
+        <x:v>Operating System / Server</x:v>
+      </x:c>
+      <x:c r="C15" s="131" t="str">
+        <x:v>対象となる技術オブジェクト</x:v>
+      </x:c>
+      <x:c r="D15" s="131" t="str">
+        <x:v>公式の Computers／Operating systems discovery 領域。</x:v>
+      </x:c>
+      <x:c r="E15" s="131" t="str">
+        <x:v>サーバー、OS クラス、基本属性テーブルを整理します。</x:v>
+      </x:c>
+      <x:c r="F15" s="131" t="str">
+        <x:v>実際のサブクラスは OS と CMDB Class Models により異なります。</x:v>
+      </x:c>
+      <x:c r="G15" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Computers.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="66" customHeight="1">
+      <x:c r="A16" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B16" s="131" t="str">
+        <x:v>Host Components</x:v>
+      </x:c>
+      <x:c r="C16" s="131" t="str">
+        <x:v>ホスト内部コンポーネント</x:v>
+      </x:c>
+      <x:c r="D16" s="131" t="str">
+        <x:v>公式のホスト収集項目に含まれる CPU、メモリ、ディスク、ファイルシステム、NIC など。</x:v>
+      </x:c>
+      <x:c r="E16" s="131" t="str">
+        <x:v>サーバー本体テーブルとコンポーネント子テーブルを分けて説明します。</x:v>
+      </x:c>
+      <x:c r="F16" s="131" t="str">
+        <x:v>独立製品モジュールとは限らず、表一覧を読みやすくするための対象整理です。</x:v>
+      </x:c>
+      <x:c r="G16" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Computers.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="66" customHeight="1">
+      <x:c r="A17" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B17" s="131" t="str">
+        <x:v>Process &amp; TCP</x:v>
+      </x:c>
+      <x:c r="C17" s="131" t="str">
+        <x:v>ランタイムデータ</x:v>
+      </x:c>
+      <x:c r="D17" s="131" t="str">
+        <x:v>公式に cmdb_running_process と cmdb_tcp が明記されています。</x:v>
+      </x:c>
+      <x:c r="E17" s="131" t="str">
+        <x:v>アプリケーション識別と Service Mapping のランタイム入力を説明します。</x:v>
+      </x:c>
+      <x:c r="F17" s="131" t="str">
+        <x:v>プロセス／TCP データだけで完全な Application Service になるわけではありません。</x:v>
+      </x:c>
+      <x:c r="G17" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/itom-visibility/r_DataCollDiscoTCPConnections.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="66" customHeight="1">
+      <x:c r="A18" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B18" s="131" t="str">
+        <x:v>Software Discovery</x:v>
+      </x:c>
+      <x:c r="C18" s="131" t="str">
+        <x:v>インストール済みソフトウェア</x:v>
+      </x:c>
+      <x:c r="D18" s="131" t="str">
+        <x:v>公式の Software discovery 領域。</x:v>
+      </x:c>
+      <x:c r="E18" s="131" t="str">
+        <x:v>ソフトウェアインストール、パッケージ、ホスト関連テーブルを整理します。</x:v>
+      </x:c>
+      <x:c r="F18" s="131" t="str">
+        <x:v>対象テーブルは SAM、Discovery コンテンツ、バージョンにより異なります。</x:v>
+      </x:c>
+      <x:c r="G18" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Software.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="66" customHeight="1">
+      <x:c r="A19" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B19" s="131" t="str">
+        <x:v>Application Discovery</x:v>
+      </x:c>
+      <x:c r="C19" s="131" t="str">
+        <x:v>アプリケーション／ミドルウェア</x:v>
+      </x:c>
+      <x:c r="D19" s="131" t="str">
+        <x:v>公式の Detailed applications と Pattern コンテンツ。</x:v>
+      </x:c>
+      <x:c r="E19" s="131" t="str">
+        <x:v>cmdb_ci_appl と製品別サブクラスを整理します。</x:v>
+      </x:c>
+      <x:c r="F19" s="131" t="str">
+        <x:v>すべてのアプリケーションを格納する単一の固定結果テーブルはありません。</x:v>
+      </x:c>
+      <x:c r="G19" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-by-itom-visibility.html?content-lang=en-US</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="66" customHeight="1">
+      <x:c r="A20" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B20" s="131" t="str">
+        <x:v>Database Discovery</x:v>
+      </x:c>
+      <x:c r="C20" s="131" t="str">
+        <x:v>データベースオブジェクト</x:v>
+      </x:c>
+      <x:c r="D20" s="131" t="str">
+        <x:v>公式の Database discovery 領域。</x:v>
+      </x:c>
+      <x:c r="E20" s="131" t="str">
+        <x:v>データベースインスタンス、Catalog、製品別サブクラス、関係を整理します。</x:v>
+      </x:c>
+      <x:c r="F20" s="131" t="str">
+        <x:v>具体的なクラスはデータベース製品と Pattern により決まります。</x:v>
+      </x:c>
+      <x:c r="G20" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/database-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="66" customHeight="1">
+      <x:c r="A21" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B21" s="131" t="str">
+        <x:v>Network Discovery</x:v>
+      </x:c>
+      <x:c r="C21" s="131" t="str">
+        <x:v>ネットワーク機器</x:v>
+      </x:c>
+      <x:c r="D21" s="131" t="str">
+        <x:v>公式の Network devices discovery 領域。</x:v>
+      </x:c>
+      <x:c r="E21" s="131" t="str">
+        <x:v>スイッチ、ルーター、ファイアウォール、LB、ポート、Network テーブルを整理します。</x:v>
+      </x:c>
+      <x:c r="F21" s="131" t="str">
+        <x:v>SNMP OID、ベンダー、機器の能力により結果が変わります。</x:v>
+      </x:c>
+      <x:c r="G21" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_NetworkDevices.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="66" customHeight="1">
+      <x:c r="A22" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B22" s="131" t="str">
+        <x:v>Storage Discovery</x:v>
+      </x:c>
+      <x:c r="C22" s="131" t="str">
+        <x:v>ストレージオブジェクト</x:v>
+      </x:c>
+      <x:c r="D22" s="131" t="str">
+        <x:v>公式の Storage discovery 領域。</x:v>
+      </x:c>
+      <x:c r="E22" s="131" t="str">
+        <x:v>Array、Pool、Volume、SAN／HBA などのテーブルを整理します。</x:v>
+      </x:c>
+      <x:c r="F22" s="131" t="str">
+        <x:v>ベンダーごとに Pattern とサブクラスが異なる場合があります。</x:v>
+      </x:c>
+      <x:c r="G22" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Storage.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="66" customHeight="1">
+      <x:c r="A23" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B23" s="131" t="str">
+        <x:v>Virtualization Discovery</x:v>
+      </x:c>
+      <x:c r="C23" s="131" t="str">
+        <x:v>仮想化プラットフォーム</x:v>
+      </x:c>
+      <x:c r="D23" s="131" t="str">
+        <x:v>公式の OS-level virtualization／VMware 関連 Discovery。</x:v>
+      </x:c>
+      <x:c r="E23" s="131" t="str">
+        <x:v>Manager、Host、VM、Cluster、Datastore、Network を整理します。</x:v>
+      </x:c>
+      <x:c r="F23" s="131" t="str">
+        <x:v>オンプレミス仮想化 Discovery と Cloud Discovery で一部オブジェクトが重複します。</x:v>
+      </x:c>
+      <x:c r="G23" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c-oslv-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="66" customHeight="1">
+      <x:c r="A24" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B24" s="131" t="str">
+        <x:v>Clustered Applications</x:v>
+      </x:c>
+      <x:c r="C24" s="131" t="str">
+        <x:v>クラスタオブジェクト</x:v>
+      </x:c>
+      <x:c r="D24" s="131" t="str">
+        <x:v>公式の Clustered application discovery。</x:v>
+      </x:c>
+      <x:c r="E24" s="131" t="str">
+        <x:v>Cluster、Node、VIP、Resource Group、アプリケーション関係を整理します。</x:v>
+      </x:c>
+      <x:c r="F24" s="131" t="str">
+        <x:v>製品固有のクラスタクラスはコンテンツパックにより変わります。</x:v>
+      </x:c>
+      <x:c r="G24" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_ClusteredAppDiscoveryOnWindows.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="66" customHeight="1">
+      <x:c r="A25" s="174" t="str">
+        <x:v>Horizontal Discovery</x:v>
+      </x:c>
+      <x:c r="B25" s="131" t="str">
+        <x:v>Container Discovery</x:v>
+      </x:c>
+      <x:c r="C25" s="131" t="str">
+        <x:v>コンテナプラットフォーム</x:v>
+      </x:c>
+      <x:c r="D25" s="131" t="str">
+        <x:v>公式の Kubernetes／Container discovery。</x:v>
+      </x:c>
+      <x:c r="E25" s="131" t="str">
+        <x:v>Cluster、Node、Namespace、Pod、Container などを整理します。</x:v>
+      </x:c>
+      <x:c r="F25" s="131" t="str">
+        <x:v>Kubernetes クラスモデルは更新が多いため、対象インスタンスで確認してください。</x:v>
+      </x:c>
+      <x:c r="G25" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/discovery/kubernetes-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="66" customHeight="1">
+      <x:c r="A26" s="178" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B26" s="131" t="str">
+        <x:v>AWS Discovery</x:v>
+      </x:c>
+      <x:c r="C26" s="131" t="str">
+        <x:v>クラウドプロバイダー</x:v>
+      </x:c>
+      <x:c r="D26" s="131" t="str">
+        <x:v>公式の AWS Cloud Discovery collected data。</x:v>
+      </x:c>
+      <x:c r="E26" s="131" t="str">
+        <x:v>AWS Account、Region、各種クラウドリソースのテーブルをまとめます。</x:v>
+      </x:c>
+      <x:c r="F26" s="131" t="str">
+        <x:v>リソース種別ではなくプロバイダー単位の中分類です。リソース種別は次の階層で展開します。</x:v>
+      </x:c>
+      <x:c r="G26" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/cloud-disco-aws-data-collected.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" customHeight="1">
+      <x:c r="A27" s="178" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B27" s="131" t="str">
+        <x:v>Microsoft Azure Discovery</x:v>
+      </x:c>
+      <x:c r="C27" s="131" t="str">
+        <x:v>クラウドプロバイダー</x:v>
+      </x:c>
+      <x:c r="D27" s="131" t="str">
+        <x:v>公式の Microsoft Azure Discovery collected data。</x:v>
+      </x:c>
+      <x:c r="E27" s="131" t="str">
+        <x:v>Subscription、Resource Group、VM、VNet、PaaS などをまとめます。</x:v>
+      </x:c>
+      <x:c r="F27" s="131" t="str">
+        <x:v>Resource Provider と Pattern バージョンが対象範囲に影響します。</x:v>
+      </x:c>
+      <x:c r="G27" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-azure-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" customHeight="1">
+      <x:c r="A28" s="178" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B28" s="131" t="str">
+        <x:v>Google Cloud Platform Discovery</x:v>
+      </x:c>
+      <x:c r="C28" s="131" t="str">
+        <x:v>クラウドプロバイダー</x:v>
+      </x:c>
+      <x:c r="D28" s="131" t="str">
+        <x:v>公式の GCP Discovery collected data。</x:v>
+      </x:c>
+      <x:c r="E28" s="131" t="str">
+        <x:v>Project、Zone、Compute、VPC、LB、GKE などをまとめます。</x:v>
+      </x:c>
+      <x:c r="F28" s="131" t="str">
+        <x:v>一部の共通クラウドクラスは他のプロバイダーでも使用されます。</x:v>
+      </x:c>
+      <x:c r="G28" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-gcp-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="66" customHeight="1">
+      <x:c r="A29" s="178" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B29" s="131" t="str">
+        <x:v>IBM Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="C29" s="131" t="str">
+        <x:v>クラウドプロバイダー</x:v>
+      </x:c>
+      <x:c r="D29" s="131" t="str">
+        <x:v>公式の IBM Cloud Discovery collected data。</x:v>
+      </x:c>
+      <x:c r="E29" s="131" t="str">
+        <x:v>Datacenter、VM、Cloud Foundry、Storage、LB などをまとめます。</x:v>
+      </x:c>
+      <x:c r="F29" s="131" t="str">
+        <x:v>対象インスタンスで有効な IBM Pattern を確認してください。</x:v>
+      </x:c>
+      <x:c r="G29" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-ibm-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="66" customHeight="1">
+      <x:c r="A30" s="178" t="str">
+        <x:v>Cloud Discovery</x:v>
+      </x:c>
+      <x:c r="B30" s="131" t="str">
+        <x:v>VMware Cloud / vCenter Discovery</x:v>
+      </x:c>
+      <x:c r="C30" s="131" t="str">
+        <x:v>クラウド／仮想化管理プラットフォーム</x:v>
+      </x:c>
+      <x:c r="D30" s="131" t="str">
+        <x:v>公式の VMware Cloud Discovery collected data。</x:v>
+      </x:c>
+      <x:c r="E30" s="131" t="str">
+        <x:v>vCenter、Host、VM、DRS、Port Group などを整理します。</x:v>
+      </x:c>
+      <x:c r="F30" s="131" t="str">
+        <x:v>Horizontal の Virtualization Discovery と一部オブジェクトが重複します。</x:v>
+      </x:c>
+      <x:c r="G30" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-vmware-cloud-disco.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="66" customHeight="1">
+      <x:c r="A31" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B31" s="131" t="str">
+        <x:v>Top-down Mapping</x:v>
+      </x:c>
+      <x:c r="C31" s="131" t="str">
+        <x:v>Entry Point から下方向に追跡</x:v>
+      </x:c>
+      <x:c r="D31" s="131" t="str">
+        <x:v>公式の Pattern-based／Top-down Service Mapping。</x:v>
+      </x:c>
+      <x:c r="E31" s="131" t="str">
+        <x:v>URL、VIP、IP:Port から Web／App／DB までの依存関係を説明します。</x:v>
+      </x:c>
+      <x:c r="F31" s="131" t="str">
+        <x:v>基礎 CI、資格情報、MID、Entry Point の品質が必要です。</x:v>
+      </x:c>
+      <x:c r="G31" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/it-operations-management/service-mapping/pattern-based-discovery.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="66" customHeight="1">
+      <x:c r="A32" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B32" s="131" t="str">
+        <x:v>Traffic-based Mapping</x:v>
+      </x:c>
+      <x:c r="C32" s="131" t="str">
+        <x:v>ランタイム通信の根拠</x:v>
+      </x:c>
+      <x:c r="D32" s="131" t="str">
+        <x:v>TCP、NetFlow、sFlow、VPC Flow Logs などから候補依存関係を推定します。</x:v>
+      </x:c>
+      <x:c r="E32" s="131" t="str">
+        <x:v>複数のトラフィック入力を同じ中分類にまとめ、小分類で展開します。</x:v>
+      </x:c>
+      <x:c r="F32" s="131" t="str">
+        <x:v>通信データは権威ある資産一覧ではなく、既存 CI との照合が必要です。</x:v>
+      </x:c>
+      <x:c r="G32" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/itom-visibility/r_DataCollDiscoTCPConnections.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="66" customHeight="1">
+      <x:c r="A33" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B33" s="131" t="str">
+        <x:v>Tag-based Mapping</x:v>
+      </x:c>
+      <x:c r="C33" s="131" t="str">
+        <x:v>タグルール</x:v>
+      </x:c>
+      <x:c r="D33" s="131" t="str">
+        <x:v>公式の Tag-based Application Service。</x:v>
+      </x:c>
+      <x:c r="E33" s="131" t="str">
+        <x:v>cmdb_key_value と cmdb_ci_service_by_tags を説明します。</x:v>
+      </x:c>
+      <x:c r="F33" s="131" t="str">
+        <x:v>タグは所属を表現できますが、ランタイム依存関係を完全には表現できません。</x:v>
+      </x:c>
+      <x:c r="G33" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" customHeight="1">
+      <x:c r="A34" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B34" s="131" t="str">
+        <x:v>CMDB-based / Manual</x:v>
+      </x:c>
+      <x:c r="C34" s="131" t="str">
+        <x:v>既存 CI の手動選択</x:v>
+      </x:c>
+      <x:c r="D34" s="131" t="str">
+        <x:v>公式の Manual Application Service。</x:v>
+      </x:c>
+      <x:c r="E34" s="131" t="str">
+        <x:v>新規資産を検出しない手動サービスモデリングを説明します。</x:v>
+      </x:c>
+      <x:c r="F34" s="131" t="str">
+        <x:v>品質は既存 CMDB と手動保守に依存します。</x:v>
+      </x:c>
+      <x:c r="G34" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="66" customHeight="1">
+      <x:c r="A35" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B35" s="131" t="str">
+        <x:v>Automated Service Suggestions</x:v>
+      </x:c>
+      <x:c r="C35" s="131" t="str">
+        <x:v>アルゴリズムによる候補サービス</x:v>
+      </x:c>
+      <x:c r="D35" s="131" t="str">
+        <x:v>既存 CI、プロセス、接続、関係を分析し、候補のサービス境界を生成します。</x:v>
+      </x:c>
+      <x:c r="E35" s="131" t="str">
+        <x:v>提案時の入力と承認後の Application Service 出力を説明します。</x:v>
+      </x:c>
+      <x:c r="F35" s="131" t="str">
+        <x:v>内部候補／アルゴリズム用テーブルはバージョンで変わるため、安定した入力と最終出力のみ掲載します。</x:v>
+      </x:c>
+      <x:c r="G35" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="66" customHeight="1">
+      <x:c r="A36" s="182" t="str">
+        <x:v>Service Mapping</x:v>
+      </x:c>
+      <x:c r="B36" s="131" t="str">
+        <x:v>Dynamic CI Group</x:v>
+      </x:c>
+      <x:c r="C36" s="131" t="str">
+        <x:v>CMDB Query による動的メンバー</x:v>
+      </x:c>
+      <x:c r="D36" s="131" t="str">
+        <x:v>公式の Query-based Service／Dynamic CI Group。</x:v>
+      </x:c>
+      <x:c r="E36" s="131" t="str">
+        <x:v>属性条件による CI の動的グループ化を説明します。</x:v>
+      </x:c>
+      <x:c r="F36" s="131" t="str">
+        <x:v>グループ化には適していますが、完全なランタイム依存関係図とは異なります。</x:v>
+      </x:c>
+      <x:c r="G36" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="66" customHeight="1">
+      <x:c r="A37" s="186" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B37" s="131" t="str">
+        <x:v>ACC Framework（ACC-F）</x:v>
+      </x:c>
+      <x:c r="C37" s="131" t="str">
+        <x:v>基本 Agent フレームワーク</x:v>
+      </x:c>
+      <x:c r="D37" s="131" t="str">
+        <x:v>Agent 登録、通信、基本ホスト、プロセス、TCP、シリアル番号データ。</x:v>
+      </x:c>
+      <x:c r="E37" s="131" t="str">
+        <x:v>ACC の基礎レイヤーとして他の ACC コンテンツと区別します。</x:v>
+      </x:c>
+      <x:c r="F37" s="131" t="str">
+        <x:v>実際のホスト CI は IRE で照合し、重複作成を避ける必要があります。</x:v>
+      </x:c>
+      <x:c r="G37" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/acc-data-collection.html?contentId=XF2OUrZDVSv4nM40Vq66bg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="66" customHeight="1">
+      <x:c r="A38" s="186" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B38" s="131" t="str">
+        <x:v>ACC Visibility Content（ACC-VC）</x:v>
+      </x:c>
+      <x:c r="C38" s="131" t="str">
+        <x:v>資産／アプリケーション可視化コンテンツ</x:v>
+      </x:c>
+      <x:c r="D38" s="131" t="str">
+        <x:v>Agent 上で Visibility Check／Pattern を実行し、拡張ホスト、アプリケーション、ファイル、証明書を収集します。</x:v>
+      </x:c>
+      <x:c r="E38" s="131" t="str">
+        <x:v>ACC の Discovery／CMDB 書き込み機能を整理します。</x:v>
+      </x:c>
+      <x:c r="F38" s="131" t="str">
+        <x:v>具体的なアプリケーションテーブルは、導入済みコンテンツパックと Pattern により決まります。</x:v>
+      </x:c>
+      <x:c r="G38" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/yokohama/it-operations-management/agent-client-collector/acc-visibility-landing-page.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="66" customHeight="1">
+      <x:c r="A39" s="186" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B39" s="131" t="str">
+        <x:v>ACC Monitoring（ACC-M）</x:v>
+      </x:c>
+      <x:c r="C39" s="131" t="str">
+        <x:v>継続メトリクス／イベント</x:v>
+      </x:c>
+      <x:c r="D39" s="131" t="str">
+        <x:v>Policy／Check により CPU、メモリ、アプリケーション、URL などを収集し、イベント／アラートを生成できます。</x:v>
+      </x:c>
+      <x:c r="E39" s="131" t="str">
+        <x:v>監視データを CMDB 資産 Discovery と分けて説明します。</x:v>
+      </x:c>
+      <x:c r="F39" s="131" t="str">
+        <x:v>メトリクス、イベント、アラートは新しい資産 CI ではありません。</x:v>
+      </x:c>
+      <x:c r="G39" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/it-operations-management/agent-client-collector/configuring-agent-client-collector-monitoring.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="66" customHeight="1">
+      <x:c r="A40" s="186" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B40" s="131" t="str">
+        <x:v>ACC Log Analytics（ACC-L）</x:v>
+      </x:c>
+      <x:c r="C40" s="131" t="str">
+        <x:v>継続ログデータ</x:v>
+      </x:c>
+      <x:c r="D40" s="131" t="str">
+        <x:v>ACC Data Input／Log Policy から Health Log Analytics へログを送信します。</x:v>
+      </x:c>
+      <x:c r="E40" s="131" t="str">
+        <x:v>ログストレージと CI コンテキストを資産テーブルから分けて説明します。</x:v>
+      </x:c>
+      <x:c r="F40" s="131" t="str">
+        <x:v>ログは HLA パイプラインに入り、通常の cmdb_ci_* には書き込まれません。</x:v>
+      </x:c>
+      <x:c r="G40" s="137" t="str">
+        <x:v>https://www.servicenow.com/docs/r/it-operations-management/agent-client-collector/hla-acc-data-input-log-policies.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="22.5" customHeight="1">
+      <x:c r="A42" s="164" t="str">
+        <x:v>3. この階層の正しい利用方法</x:v>
+      </x:c>
+      <x:c r="B42" s="164"/>
+      <x:c r="C42" s="164"/>
+      <x:c r="D42" s="164"/>
+    </x:row>
+    <x:row r="43" ht="31.5" customHeight="1">
+      <x:c r="A43" s="170" t="str">
+        <x:v>階層</x:v>
+      </x:c>
+      <x:c r="B43" s="170" t="str">
+        <x:v>本資料での意味</x:v>
+      </x:c>
+      <x:c r="C43" s="170" t="str">
+        <x:v>意味しないこと</x:v>
+      </x:c>
+      <x:c r="D43" s="170" t="str">
+        <x:v>推奨する使い方</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="54.75" customHeight="1">
+      <x:c r="A44" s="174" t="str">
+        <x:v>大分類</x:v>
+      </x:c>
+      <x:c r="B44" s="131" t="str">
+        <x:v>4つの主要な Discovery、Mapping、Agent データ収集能力。</x:v>
+      </x:c>
+      <x:c r="C44" s="131" t="str">
+        <x:v>4方式が相互に代替できることを意味しません。</x:v>
+      </x:c>
+      <x:c r="D44" s="131" t="str">
+        <x:v>機能選定と全体アーキテクチャ比較に使用します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="54.75" customHeight="1">
+      <x:c r="A45" s="174" t="str">
+        <x:v>中分類</x:v>
+      </x:c>
+      <x:c r="B45" s="131" t="str">
+        <x:v>起点、技術オブジェクト、クラウドプラットフォーム、Mapping 方法、ACC コンポーネントによる調査索引。</x:v>
+      </x:c>
+      <x:c r="C45" s="131" t="str">
+        <x:v>ServiceNow の統一製品ツリーでも CMDB 継承階層でもありません。</x:v>
+      </x:c>
+      <x:c r="D45" s="131" t="str">
+        <x:v>収集範囲と関連テーブルグループの特定に使用します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="54.75" customHeight="1">
+      <x:c r="A46" s="174" t="str">
+        <x:v>小分類／対象</x:v>
+      </x:c>
+      <x:c r="B46" s="131" t="str">
+        <x:v>中分類をさらに具体化したオブジェクト、Pattern、入力方式、データタイプ。</x:v>
+      </x:c>
+      <x:c r="C46" s="131" t="str">
+        <x:v>すべての中分類に小分類が存在するとは限りません。</x:v>
+      </x:c>
+      <x:c r="D46" s="131" t="str">
+        <x:v>特定の cmdb_ci_* や実行テーブルが現れる理由の説明に使用します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="54.75" customHeight="1">
+      <x:c r="A47" s="174" t="str">
+        <x:v>物理テーブル</x:v>
+      </x:c>
+      <x:c r="B47" s="131" t="str">
+        <x:v>最終的な書き込み先、参照先、実行時に関係する ServiceNow テーブル。</x:v>
+      </x:c>
+      <x:c r="C47" s="131" t="str">
+        <x:v>各実行で掲載テーブルのすべてが書き込まれることを意味しません。</x:v>
+      </x:c>
+      <x:c r="D47" s="131" t="str">
+        <x:v>対象インスタンスのバージョン、プラグイン、Pattern、Dictionary で確認します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="54.75" customHeight="1">
+      <x:c r="A48" s="174" t="str">
+        <x:v>根拠レベル</x:v>
+      </x:c>
+      <x:c r="B48" s="131" t="str">
+        <x:v>A は公式にテーブル名が明記、B は公式対象範囲と標準クラスモデルによる整理、C は補助資料による相互確認。</x:v>
+      </x:c>
+      <x:c r="C48" s="131" t="str">
+        <x:v>製品機能の成熟度や重要度の評価ではありません。</x:v>
+      </x:c>
+      <x:c r="D48" s="131" t="str">
+        <x:v>アーキテクチャ判断では A を優先し、B／C は対象インスタンスで検証して使用します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="43.5" customHeight="1">
+      <x:c r="A50" s="157" t="str">
+        <x:v>推奨：「中分類」は調査・検索用の索引として利用してください。製品範囲とライセンスの判断は公式機能資料へ戻り、テーブル設計では対象インスタンスの Pattern、CMDB CI Class Models、System Definition &gt; Tables／Dictionary、IRE／Reconciliation 設定を確認してください。</x:v>
+      </x:c>
+      <x:c r="B50" s="157"/>
+      <x:c r="C50" s="157"/>
+      <x:c r="D50" s="157"/>
+      <x:c r="E50" s="157"/>
+      <x:c r="F50" s="157"/>
+      <x:c r="G50" s="157"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
+    <x:mergeCell ref="A12:G12"/>
+    <x:mergeCell ref="A42:D42"/>
+    <x:mergeCell ref="A50:G50"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref5bb0d927974d19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ServiceNow_Discovery_ACC_Data_Inventory_JA.xlsx
+++ b/ServiceNow_Discovery_ACC_Data_Inventory_JA.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery_ACCデータ一覧" sheetId="1" r:id="R759b1710ce9145e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP Rangeテーブル調査" sheetId="2" r:id="R98028f52e1664542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4方式横断比較" sheetId="3" r:id="R5b7242274a154d77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中分類の分類基準" sheetId="4" r:id="R96e3a6555a3147fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery_ACCデータ一覧" sheetId="1" r:id="Rfc82990272e74b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP Rangeテーブル調査" sheetId="2" r:id="R9d4408fee6184f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4方式横断比較" sheetId="3" r:id="Rf1bedf4fa1904a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中分類の分類基準" sheetId="4" r:id="Re2cf008dcff1486c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="21">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -135,6 +135,11 @@
       <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="8"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Yu Gothic"/>
     </x:font>
   </x:fonts>
   <x:fills count="38">
@@ -373,7 +378,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="187">
+  <x:cellXfs count="189">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -838,6 +843,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="37" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1088,7 +1099,7 @@
     <x:col min="3" max="3" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="29.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="41.25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="43.75" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28.75" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="9.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="33.130001068115234" hidden="0" customWidth="1"/>
@@ -1126,9 +1137,9 @@
       <x:c r="J2" s="8"/>
       <x:c r="K2" s="8"/>
     </x:row>
-    <x:row r="3" ht="40.5" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>見方：A＝公式ページにテーブル名／フィールドが明記されているもの。B＝収集範囲は公式に明記されているが、テーブル名は標準 CMDB クラスモデルと Pattern に基づく整理のため、対象インスタンスでの確認が必要です。IP Range は Discovery の入口であり、固定の CI テーブルには対応しません。ServiceNow Australia ドキュメント体系を基準に整理。作成日：2026-06-11。</x:v>
+        <x:v>見方：A＝公式ページにテーブル名／フィールドが明記されているもの。B＝収集範囲は公式に明記されているが、テーブル名は標準 CMDB クラスモデルと Pattern に基づく整理のため、対象インスタンスでの確認が必要です。第5列は「主要な対象 CI」「継承元／フィールド定義テーブル」「関連明細／実行時データ」「条件付き／製品固有テーブル」に分けて記載しています。同一テーブルが役割の違いにより複数行に現れる場合があります。また、親テーブルの記載は別の CI レコードが追加作成されることを意味しません。IP Range は Discovery の入口であり、固定の CI テーブルには対応しません。ServiceNow Australia ドキュメント体系を基準に整理。更新日：2026-06-11。</x:v>
       </x:c>
       <x:c r="B3" s="12"/>
       <x:c r="C3" s="12"/>
@@ -1170,8 +1181,8 @@
       <x:c r="E5" s="19" t="str">
         <x:v>4. 収集データ</x:v>
       </x:c>
-      <x:c r="F5" s="19" t="str">
-        <x:v>5. 主な書き込み先／関連テーブル</x:v>
+      <x:c r="F5" s="187" t="str">
+        <x:v>5. 主な書き込み先／関連テーブル（対象 CI／継承元／関連明細／条件付き項目）</x:v>
       </x:c>
       <x:c r="G5" s="19" t="str">
         <x:v>リレーション／実行記録／補助テーブル</x:v>
@@ -1189,7 +1200,7 @@
         <x:v>公式 URL</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="75.75" customHeight="1">
+    <x:row r="6" ht="177" customHeight="1">
       <x:c r="A6" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1206,9 +1217,23 @@
       <x:c r="E6" s="24" t="str">
         <x:v>到達可能性、開いているポート、デバイスの種類、資格情報が利用可能かどうか。次に、各リソース タイプの詳細なコレクションを入力します。</x:v>
       </x:c>
-      <x:c r="F6" s="24" t="str">
-        <x:v>このステップには、固定の cmdb_ci_* ターゲット テーブルがありません。
-どの CI テーブルが最終的に書き込まれるかは、特定されたサーバー、ネットワーク、ストレージ、アプリケーションなどのタイプによって異なります (以下の行を参照)。</x:v>
+      <x:c r="F6" s="188" t="str">
+        <x:v>【対象範囲・スケジュール（参照／実行時更新）】
+discovery_schedule
+discovery_range_item
+discovery_range_item_ip
+ip_address_range
+ip_exclusion
+【スキャン・分類・コンテンツ（参照／条件付きで関連）】
+cmdb_ip_service
+discovery_port_probe
+discovery_classy
+discovery_class_criteria
+discovery_probes
+discovery_sensor
+sa_pattern
+【最終的な CMDB 対象】
+固定の cmdb_ci_* テーブルはありません。分類結果、Pattern、対象デバイスの種類によって決まります。</x:v>
       </x:c>
       <x:c r="G6" s="24" t="str">
         <x:v>discovery_status
@@ -1229,7 +1254,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-by-itom-visibility.html?content-lang=en-US</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="109.5" customHeight="1">
+    <x:row r="7" ht="307.5" customHeight="1">
       <x:c r="A7" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1246,15 +1271,38 @@
       <x:c r="E7" s="24" t="str">
         <x:v>ホスト名、FQDN、OS/バージョン、CPU、メモリ、シリアル番号、IP、ネットワークカード、デフォルトゲートウェイ、起動時間など</x:v>
       </x:c>
-      <x:c r="F7" s="24" t="str">
-        <x:v>cmdb_ci_computer
-cmdb_ci_server
+      <x:c r="F7" s="188" t="str">
+        <x:v>【主要な対象 CI クラス】
 cmdb_ci_win_server
 cmdb_ci_linux_server
+cmdb_ci_aix_server
+cmdb_ci_hpux_server
+cmdb_ci_solaris_server
 cmdb_ci_unix_server
+cmdb_ci_computer（一部のエンドポイント／macOS。リリースごとに要確認）
+【継承元／フィールド定義テーブル】
+cmdb_ci
+cmdb_ci_hardware
+cmdb_ci_computer
+cmdb_ci_server
+【同一 OS Discovery で関連して更新される可能性があるテーブル】
+cmdb_ci_disk
+cmdb_ci_file_system
+cmdb_ci_network_adapter
 cmdb_ci_ip_address
-cmdb_ci_network_adapter
-cmdb_ci_dns_name</x:v>
+cmdb_ci_dns_name
+cmdb_serial_number
+cmdb_running_process
+cmdb_ci_patches
+【条件付き：OS 内部の仮想化】
+cmdb_ci_kvm
+cmdb_ci_kvm_vm_instance
+cmdb_ci_kvm_object
+cmdb_ci_kvm_network
+cmdb_ci_kvm_storage_pool
+cmdb_kvm_device
+cmdb_ci_solaris_instance
+cmdb_ci_vm_zones（Solaris Zones の旧クラス。Australia のクラス説明では廃止扱い）</x:v>
       </x:c>
       <x:c r="G7" s="24" t="str">
         <x:v>cmdb_serial_number
@@ -1273,7 +1321,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Computers.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="87" customHeight="1">
+    <x:row r="8" ht="204" customHeight="1">
       <x:c r="A8" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1290,13 +1338,26 @@
       <x:c r="E8" s="24" t="str">
         <x:v>CPU/コア、メモリモジュール、ディスク、ファイルシステム、マウントポイント、NIC、MAC、IP、シリアル番号など</x:v>
       </x:c>
-      <x:c r="F8" s="24" t="str">
-        <x:v>cmdb_ci_cpu
-cmdb_ci_memory_module
+      <x:c r="F8" s="188" t="str">
+        <x:v>【直接更新されるコンポーネント／ネットワーク明細】
 cmdb_ci_disk
 cmdb_ci_file_system
 cmdb_ci_network_adapter
-cmdb_ci_ip_address</x:v>
+cmdb_ci_ip_address
+cmdb_ci_dns_name
+cmdb_serial_number
+【条件付き更新：プラットフォームまたは Pattern が対応する場合】
+cmdb_ci_cpu
+cmdb_ci_memory_module
+cmdb_ci_storage_hba
+cmdb_ci_fc_hba
+cmdb_ci_fc_port
+cmdb_ci_fc_disk
+cmdb_ci_iscsi_disk
+【一部のハードウェア属性は親／ホストクラスに直接保持】
+cmdb_ci_hardware
+cmdb_ci_computer
+各 OS Server サブクラス</x:v>
       </x:c>
       <x:c r="G8" s="24" t="str">
         <x:v>cmdb_serial_number
@@ -1315,7 +1376,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Computers.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="64.5" customHeight="1">
+    <x:row r="9" ht="105" customHeight="1">
       <x:c r="A9" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1332,8 +1393,15 @@
       <x:c r="E9" s="24" t="str">
         <x:v>プロセス名、PID、コマンド ライン、ポート、プロトコル、ローカル/リモート アドレス、プロセスと接続の関連付け。</x:v>
       </x:c>
-      <x:c r="F9" s="24" t="str">
-        <x:v>新しいインフラストラクチャ cmdb_ci_* は通常、直接作成されません。これは主に、アプリケーション CI を識別し、依存関係を確立するために使用されます。</x:v>
+      <x:c r="F9" s="188" t="str">
+        <x:v>【公式資料に明記された実行時テーブル】
+cmdb_running_process
+cmdb_tcp
+【条件付きで関連／後続モデリング】
+cmdb_ip_service
+cmdb_ci_appl および製品別サブクラス
+cmdb_rel_ci
+注：プロセスと TCP のレコードは通常、アプリケーション識別、ADM、Service Mapping の入力です。接続ごとに新しい技術 CI が作成されることを意味しません。</x:v>
       </x:c>
       <x:c r="G9" s="24" t="str">
         <x:v>cmdb_running_process
@@ -1353,7 +1421,7 @@
         <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/itom-visibility/r_DataCollDiscoTCPConnections.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="64.5" customHeight="1">
+    <x:row r="10" ht="114" customHeight="1">
       <x:c r="A10" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1370,10 +1438,16 @@
       <x:c r="E10" s="24" t="str">
         <x:v>ソフトウェア名、バージョン、製造元、インストール パス、インストール日、ソフトウェア パッケージとホストの関連付け。</x:v>
       </x:c>
-      <x:c r="F10" s="24" t="str">
-        <x:v>cmdb_sam_sw_install
+      <x:c r="F10" s="188" t="str">
+        <x:v>【主なソフトウェア結果】
+cmdb_sam_sw_install
 cmdb_ci_spkg
-(使用はSAM/ディスカバリーコンテンツのバージョンによって異なります)</x:v>
+cmdb_software_instance（旧方式／移行前のテーブル。現在は通常 cmdb_sam_sw_install へ移行）
+【関連オブジェクト】
+cmdb_ci_computer／各 OS Server サブクラス
+cmdb_running_process（プロセス証跡）
+cmdb_rel_ci
+注：インストールレコード、ソフトウェアパッケージ、ソフトウェアインスタンステーブルのどれを使用するかは、SAM、Discovery Content、リリースによって異なります。</x:v>
       </x:c>
       <x:c r="G10" s="24" t="str">
         <x:v>cmdb_rel_ci</x:v>
@@ -1391,7 +1465,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Software.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="64.5" customHeight="1">
+    <x:row r="11" ht="123" customHeight="1">
       <x:c r="A11" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1408,9 +1482,17 @@
       <x:c r="E11" s="24" t="str">
         <x:v>製品タイプ、バージョン、インストール ディレクトリ、リスニング ポート、構成、インスタンス、ホスト、上流および下流の依存関係。</x:v>
       </x:c>
-      <x:c r="F11" s="24" t="str">
-        <x:v>cmdb_ci_appl およびそのサブクラス
-（例：Web Server、Application Server、Middleware の製品別サブクラス）</x:v>
+      <x:c r="F11" s="188" t="str">
+        <x:v>【アプリケーション基底クラス／主要な対象】
+cmdb_ci_appl
+製品固有の cmdb_ci_appl サブクラス（Pattern の Identification Section で指定）
+【関連する Discovery データ】
+cmdb_running_process
+cmdb_tcp
+cmdb_ci_computer／cmdb_ci_server
+cmdb_ci_database／cmdb_ci_db_instance（アプリケーションがデータベースを使用する場合）
+cmdb_rel_ci
+注：Web Server、Application Server、Middleware に共通する単一の結果テーブルはありません。インストール済み Pattern の対象 CI Class を基準に確認します。</x:v>
       </x:c>
       <x:c r="G11" s="24" t="str">
         <x:v>cmdb_running_process
@@ -1430,7 +1512,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-by-itom-visibility.html?content-lang=en-US</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="64.5" customHeight="1">
+    <x:row r="12" ht="213" customHeight="1">
       <x:c r="A12" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1447,11 +1529,26 @@
       <x:c r="E12" s="24" t="str">
         <x:v>データベース製品、バージョン、インスタンス、カタログ/スキーマ、ポート、ホスト、クラスター、およびアプリケーションの関係。</x:v>
       </x:c>
-      <x:c r="F12" s="24" t="str">
-        <x:v>cmdb_ci_database
+      <x:c r="F12" s="188" t="str">
+        <x:v>【共通データベースクラス】
+cmdb_ci_database
 cmdb_ci_db_instance
 cmdb_ci_db_catalog
-および製品固有のデータベース サブクラス</x:v>
+【製品固有サブクラスの例：MSSQL】
+cmdb_ci_db_mssql_instance
+cmdb_ci_db_mssql_database
+cmdb_ci_mssql_cluster
+cmdb_ci_mssql_cluster_node
+cmdb_ci_mssql_ag
+cmdb_ci_mssql_ag_replica
+cmdb_ci_mssql_ag_listener
+mssql_sqlservice_info
+mssql_components_info
+【関連データ】
+cmdb_running_process
+cmdb_tcp
+cmdb_rel_ci
+Oracle、MySQL、PostgreSQL、DB2 などは、それぞれの Pattern で指定されたデータベースサブクラスを使用します。</x:v>
       </x:c>
       <x:c r="G12" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1471,7 +1568,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/database-discovery.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="109.5" customHeight="1">
+    <x:row r="13" ht="240" customHeight="1">
       <x:c r="A13" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1488,15 +1585,30 @@
       <x:c r="E13" s="24" t="str">
         <x:v>デバイス モデル/シリアル番号/OS、インターフェイスとポート、IP/MAC、ルーティング、VLAN、隣接関係、およびトポロジ。</x:v>
       </x:c>
-      <x:c r="F13" s="24" t="str">
-        <x:v>cmdb_ci_netgear
+      <x:c r="F13" s="188" t="str">
+        <x:v>【主要なネットワーク CI】
+cmdb_ci_netgear
 cmdb_ci_ip_switch
 cmdb_ci_ip_router
 cmdb_ci_ip_firewall
 cmdb_ci_lb
 cmdb_ci_network_port
+cmdb_ci_network_adapter
 cmdb_ci_ip_address
-cmdb_ci_network</x:v>
+cmdb_ci_network
+cmdb_ci_ip_network
+cmdb_ip_service
+【Layer 2／ARP／ネイバー処理テーブル】
+dscy_router_interface
+dscy_switchport
+discovery_device_neighbors
+discovery_net_arp_table
+discovery_switch_bridge_port_table
+discovery_switch_spanning_tree_table
+discovery_switch_fwd_table
+dscy_net_base
+【リレーション】
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G13" s="24" t="str">
         <x:v>cmdb_rel_ci</x:v>
@@ -1514,7 +1626,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_NetworkDevices.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="109.5" customHeight="1">
+    <x:row r="14" ht="204" customHeight="1">
       <x:c r="A14" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1531,15 +1643,25 @@
       <x:c r="E14" s="24" t="str">
         <x:v>ストレージ システム、アレイ、プール、ボリューム、ディスク、ファイル システム、FC HBA/ポート、および容量の関係。</x:v>
       </x:c>
-      <x:c r="F14" s="24" t="str">
-        <x:v>cmdb_ci_storage_server
+      <x:c r="F14" s="188" t="str">
+        <x:v>【ストレージシステム／論理リソース】
+cmdb_ci_storage_server
 cmdb_ci_storage_array
 cmdb_ci_storage_pool
 cmdb_ci_storage_volume
+cmdb_ci_storage_vol_snapshot
 cmdb_ci_disk
 cmdb_ci_file_system
+【SAN／HBA／ポート／ディスク】
+cmdb_ci_storage_hba
 cmdb_ci_fc_hba
-cmdb_ci_fc_port</x:v>
+cmdb_ci_fc_port
+cmdb_ci_fc_disk
+cmdb_ci_iscsi_disk
+【条件付き項目】
+ベンダー固有の Storage／SAN サブクラス
+cmdb_rel_ci
+注：ホスト側ストレージ、SMI-S／CIM、ベンダー API では対象クラスが異なります。実際の Pattern 出力を基準に確認します。</x:v>
       </x:c>
       <x:c r="G14" s="24" t="str">
         <x:v>cmdb_rel_ci</x:v>
@@ -1557,7 +1679,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_Storage.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="98.25" customHeight="1">
+    <x:row r="15" ht="307.5" customHeight="1">
       <x:c r="A15" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1574,14 +1696,42 @@
       <x:c r="E15" s="24" t="str">
         <x:v>仮想化マネージャー、データセンター、クラスター、ホスト、VM、テンプレート、データストレージ、ネットワーク、所有権関係。</x:v>
       </x:c>
-      <x:c r="F15" s="24" t="str">
-        <x:v>cmdb_ci_vcenter
+      <x:c r="F15" s="188" t="str">
+        <x:v>【共通仮想化親クラス】
+cmdb_ci_virtualization_server
+cmdb_ci_vm_instance
+cmdb_ci_vm_object
+【VMware／vCenter】
+cmdb_ci_vcenter
+cmdb_ci_vcenter_datacenter
+cmdb_ci_vcenter_cluster
 cmdb_ci_esx_server
-cmdb_ci_vm_instance
 cmdb_ci_vmware_instance
-cmdb_ci_vcenter_cluster
+cmdb_ci_vmware_template
 cmdb_ci_vcenter_datastore
-cmdb_ci_vcenter_network</x:v>
+cmdb_ci_vcenter_network
+cmdb_ci_vcenter_folder
+cmdb_ci_vcenter_dv_port_group
+cmdb_ci_esx_resource_pool
+cmdb_ci_vmware_nic
+vcenter_datastore_hostmount
+cmdb_ci_vcenter_datastore_disk
+【Hyper-V】
+cmdb_ci_hyper_v_server
+cmdb_ci_hyper_v_instance
+cmdb_ci_hyper_v_network
+cmdb_ci_hyper_v_resource_pool
+cmdb_ci_hyper_v_rpool_comp
+cmdb_ci_hyper_v_cluster
+【Linux KVM】
+cmdb_ci_kvm
+cmdb_ci_kvm_vm_instance
+cmdb_ci_kvm_object
+cmdb_ci_kvm_network
+cmdb_ci_kvm_storage_pool
+cmdb_ci_kvm_storage_volume
+cmdb_kvm_device
+【リレーション】cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G15" s="24" t="str">
         <x:v>cmdb_rel_ci</x:v>
@@ -1599,7 +1749,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c-oslv-discovery.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="64.5" customHeight="1">
+    <x:row r="16" ht="141" customHeight="1">
       <x:c r="A16" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1616,10 +1766,19 @@
       <x:c r="E16" s="24" t="str">
         <x:v>クラスター名、ノード、仮想 IP、リソース グループ、クラスター アプリケーション/データベース、およびノー​​ドの関係。</x:v>
       </x:c>
-      <x:c r="F16" s="24" t="str">
-        <x:v>cmdb_ci_cluster
+      <x:c r="F16" s="188" t="str">
+        <x:v>【共通クラスタクラス】
+cmdb_ci_cluster
 cmdb_ci_cluster_node
-および製品固有のクラスター サブクラス</x:v>
+【Windows Server Cluster の公式記載テーブル】
+cmdb_ci_win_cluster
+cmdb_ci_win_cluster_resource
+cmdb_ci_win_cluster_node
+cmdb_ci_cluster_node_resource
+cmdb_ci_cluster_vip
+【製品固有のアプリケーションクラスタ】
+データベース／ミドルウェア Pattern で指定される Cluster、Node、Listener、Resource サブクラス
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G16" s="24" t="str">
         <x:v>cmdb_rel_ci</x:v>
@@ -1637,7 +1796,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/c_ClusteredAppDiscoveryOnWindows.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="98.25" customHeight="1">
+    <x:row r="17" ht="249" customHeight="1">
       <x:c r="A17" s="32" t="str">
         <x:v>Horizontal Discovery
 （水平ディスカバリ）</x:v>
@@ -1654,14 +1813,30 @@
       <x:c r="E17" s="24" t="str">
         <x:v>クラスター、ノード、名前空間、ポッド、コンテナー、イメージ、サービス、ワークロード、相互関係。</x:v>
       </x:c>
-      <x:c r="F17" s="24" t="str">
-        <x:v>cmdb_ci_kubernetes_cluster
+      <x:c r="F17" s="188" t="str">
+        <x:v>【Kubernetes コアクラス】
+cmdb_ci_kubernetes_cluster
 cmdb_ci_kubernetes_node
 cmdb_ci_kubernetes_namespace
 cmdb_ci_kubernetes_pod
-cmdb_ci_container
-cmdb_ci_container_image
-および Kubernetes ワークロードのサブクラス</x:v>
+cmdb_ci_kubernetes_service
+cmdb_ci_kubernetes_volume
+cmdb_ci_kubernetes_workload
+【ワークロードサブクラス】
+cmdb_ci_kubernetes_deployment
+cmdb_ci_kubernetes_replicaset
+cmdb_ci_kubernetes_daemonset
+cmdb_ci_kubernetes_statefulset
+cmdb_ci_kubernetes_job
+cmdb_ci_kubernetes_cronjob
+【コンテナ／イメージ／リポジトリ】
+cmdb_ci_docker_container
+cmdb_ci_docker_image
+cmdb_ci_container_repository
+cmdb_ci_container_repository_entry
+【タグとリレーション】
+cmdb_key_value
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G17" s="24" t="str">
         <x:v>cmdb_rel_ci</x:v>
@@ -1679,7 +1854,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/discovery/kubernetes-discovery.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="177" customHeight="1">
+    <x:row r="18" ht="240" customHeight="1">
       <x:c r="A18" s="39" t="str">
         <x:v>Cloud Discovery
 （クラウドディスカバリ）</x:v>
@@ -1696,8 +1871,9 @@
       <x:c r="E18" s="24" t="str">
         <x:v>リージョン/AZ、EC2、AMI/テンプレート、セキュリティグループ、VPC/サブネット/NIC/EIP、EBS、ELB、S3、RDS、Webサービス、EKSなど。</x:v>
       </x:c>
-      <x:c r="F18" s="24" t="str">
-        <x:v>cmdb_ci_aws_datacenter
+      <x:c r="F18" s="188" t="str">
+        <x:v>【AWS 公式データ収集ページに記載された主要 CI テーブル】
+cmdb_ci_aws_datacenter
 cmdb_ci_availability_zone
 cmdb_ci_vm_instance
 cmdb_ci_compute_security_group
@@ -1708,9 +1884,18 @@
 cmdb_ci_cloud_subnet
 cmdb_ci_nic
 cmdb_ci_cloud_load_balancer
+cmdb_ci_resource_group
+cmdb_ci_cloud_public_ipaddress
+cmdb_ci_cloud_storage_account
+cmdb_ci_dns_alias
+cmdb_ci_dns_name
 cmdb_ci_cloud_database
-cmdb_ci_cloud_storage_account
-cmdb_ci_kubernetes_cluster</x:v>
+cmdb_ci_cloud_webserver
+cmdb_ci_kubernetes_cluster
+【共通のデータソース／タグ／リレーション】
+cmdb_ci_cloud_service_account
+cmdb_key_value
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G18" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1729,7 +1914,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/cloud-disco-aws-data-collected.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="177" customHeight="1">
+    <x:row r="19" ht="276" customHeight="1">
       <x:c r="A19" s="39" t="str">
         <x:v>Cloud Discovery
 （クラウドディスカバリ）</x:v>
@@ -1746,21 +1931,34 @@
       <x:c r="E19" s="24" t="str">
         <x:v>リージョン、VM、イメージ/仕様、セキュリティ グループ、VNet/サブネット/NIC/パブリック IP、負荷分散、ストレージ アカウント、SQL、Web アプリ、デプロイ、リソース グループなど。</x:v>
       </x:c>
-      <x:c r="F19" s="24" t="str">
-        <x:v>cmdb_ci_vm_instance
+      <x:c r="F19" s="188" t="str">
+        <x:v>【Azure 公式データ収集ページに記載された主要 CI テーブル】
+cmdb_ci_azure_datacenter
+cmdb_ci_availability_zone
+cmdb_ci_vm_instance
 cmdb_ci_compute_security_group
-cmdb_ci_compute_template
-cmdb_ci_hardware_type
+cmdb_ci_os_template
+cmdb_ci_storage_volume
 cmdb_ci_network
 cmdb_ci_cloud_subnet
 cmdb_ci_nic
 cmdb_ci_cloud_load_balancer
-cmdb_ci_azure_deployment
+cmdb_ci_azure_deployment（対応プラグインが必要）
 cmdb_ci_resource_group
 cmdb_ci_cloud_public_ipaddress
 cmdb_ci_cloud_storage_account
 cmdb_ci_cloud_database
-cmdb_ci_cloud_webserver</x:v>
+cmdb_ci_cloud_webserver
+cmdb_ci_ip_address
+cmdb_ci_database
+cmdb_ci_compute_template
+cmdb_ci_hardware_type
+【Top-down Service Mapping のみで使用される条件付き項目】
+cmdb_ci_lb_service
+【共通のデータソース／タグ／リレーション】
+cmdb_ci_cloud_service_account
+cmdb_key_value
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G19" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1780,7 +1978,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-azure-discovery.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="177" customHeight="1">
+    <x:row r="20" ht="249" customHeight="1">
       <x:c r="A20" s="39" t="str">
         <x:v>Cloud Discovery
 （クラウドディスカバリ）</x:v>
@@ -1797,13 +1995,20 @@
       <x:c r="E20" s="24" t="str">
         <x:v>プロジェクト/リージョン/ゾーン、Compute Engine、テンプレート、ディスク、VPC/サブネット、ファイアウォール、負荷分散サービス/プール/メンバー/ヘルスチェック、GKE など。</x:v>
       </x:c>
-      <x:c r="F20" s="24" t="str">
-        <x:v>cmdb_ci_vm_instance
+      <x:c r="F20" s="188" t="str">
+        <x:v>【GCP 公式データ収集ページに記載された主要 CI テーブル】
+cmdb_ci_google_datacenter
+cmdb_ci_availability_zone
+cmdb_ci_vm_instance
+cmdb_ci_storage_volume
+cmdb_ci_storage_vol_snapshot
+cmdb_ci_cloud_public_ipaddress
 cmdb_ci_compute_template
-cmdb_ci_storage_volume
+cmdb_ci_instance_template
+cmdb_ci_disk_type
+cmdb_ci_cloud_subnet
+cmdb_ci_os_template
 cmdb_ci_network
-cmdb_ci_cloud_subnet
-cmdb_ci_nic
 cmdb_ci_cloud_load_balancer
 cmdb_ci_lb_service
 cmdb_ci_lb_health_service
@@ -1811,7 +2016,11 @@
 cmdb_ci_lb_pool_member
 cmdb_ci_network_acl
 cmdb_ci_network_acl_rule
-cmdb_ci_kubernetes_cluster</x:v>
+cmdb_ci_kubernetes_cluster
+【共通のデータソース／タグ／リレーション】
+cmdb_ci_cloud_service_account
+cmdb_key_value
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G20" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1830,7 +2039,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-gcp-discovery.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="165.75" customHeight="1">
+    <x:row r="21" ht="213" customHeight="1">
       <x:c r="A21" s="39" t="str">
         <x:v>Cloud Discovery
 （クラウドディスカバリ）</x:v>
@@ -1847,8 +2056,11 @@
       <x:c r="E21" s="24" t="str">
         <x:v>データセンター、VM、イメージ、セキュリティ グループ、NIC、ボリューム/スナップショット、キー ペア、サービス アカウント、Cloud Foundry 組織/スペース、LB など。</x:v>
       </x:c>
-      <x:c r="F21" s="24" t="str">
-        <x:v>cmdb_ci_ibm_datacenter
+      <x:c r="F21" s="188" t="str">
+        <x:v>【IBM Cloud 公式データ収集ページに記載された主要 CI テーブル】
+cmdb_ci_cloud_service_account
+cmdb_ci_ibm_datacenter
+cmdb_ci_availability_zone
 cmdb_ci_vm_instance
 cmdb_ci_nic
 cmdb_ci_os_template
@@ -1856,11 +2068,16 @@
 cmdb_ci_storage_volume
 cmdb_ci_storage_vol_snapshot
 cmdb_ci_cloud_key_pair
-cmdb_ci_cloud_service_account
 cmdb_ci_cloud_org
 cmdb_ci_cloud_space
 cmdb_ci_cloud_load_balancer
-cmdb_ci_lb_service</x:v>
+cmdb_ci_lb_service
+cmdb_ci_lb_pool
+cmdb_ci_lb_pool_member
+cmdb_ci_lb_health_service
+【タグとリレーション】
+cmdb_key_value
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G21" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1879,7 +2096,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-ibm-discovery.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="109.5" customHeight="1">
+    <x:row r="22" ht="307.5" customHeight="1">
       <x:c r="A22" s="39" t="str">
         <x:v>Cloud Discovery
 （クラウドディスカバリ）</x:v>
@@ -1896,15 +2113,41 @@
       <x:c r="E22" s="24" t="str">
         <x:v>vCenter オブジェクト、VM/ホスト グループ、DRS ルール/構成、分散ポート グループ、ネットワーク、データストア、および VM。</x:v>
       </x:c>
-      <x:c r="F22" s="24" t="str">
-        <x:v>cmdb_ci_vmware_instance
+      <x:c r="F22" s="188" t="str">
+        <x:v>【vCenter／構成階層／DRS】
+cmdb_ci_vcenter
+cmdb_ci_vcenter_datacenter
+cmdb_ci_vcenter_cluster
+cmdb_ci_vcenter_folder
 cmdb_ci_vcenter_vm_group
 cmdb_ci_vcenter_host_group
 cmdb_ci_vcenter_cluster_drs_rule
 cmdb_ci_drs_vm_config
+【VM／テンプレート／ホスト】
+cmdb_ci_vm_instance（親クラス）
+cmdb_ci_vmware_instance
+cmdb_ci_vmware_template
+cmdb_ci_esx_server
+cmdb_ci_esx_resource_pool
+【ネットワーク／ストレージ】
+cmdb_ci_vcenter_network
 cmdb_ci_vcenter_dv_port_group
-cmdb_ci_vcenter_network
-および他の vCenter サブクラス</x:v>
+cmdb_ci_vcenter_datastore
+cmdb_ci_vcenter_datastore_disk
+vcenter_datastore_hostmount
+cmdb_ci_vmware_nic
+cmdb_ci_network_adapter
+cmdb_ci_storage_volume
+cmdb_ci_disk
+cmdb_ci_storage_hba
+cmdb_ci_fc_port
+cmdb_ci_fc_disk
+cmdb_ci_iscsi_disk
+【条件付き：SAM／タグ／リレーション】
+samp_vmware_license_key
+samp_vmware_license_key_usage
+cmdb_key_value
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G22" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1923,7 +2166,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-vmware-cloud-disco.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="64.5" customHeight="1">
+    <x:row r="23" ht="150" customHeight="1">
       <x:c r="A23" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -1940,10 +2183,20 @@
       <x:c r="E23" s="24" t="str">
         <x:v>アプリケーション サービス、それをホストするアプリケーション/サーバー/ネットワーク/データベース CI、およびそれらの依存関係トポロジ。</x:v>
       </x:c>
-      <x:c r="F23" s="24" t="str">
-        <x:v>cmdb_ci_service_discovered
-cmdb_ci_service_auto
-そして、Patternによって識別されるさまざまな cmdb_ci_*</x:v>
+      <x:c r="F23" s="188" t="str">
+        <x:v>【Application Service の対象クラス】
+cmdb_ci_service_discovered
+cmdb_ci_service_auto（親クラス／リリース依存）
+【メンバー CI：参照・再利用、または Pattern による条件付き更新】
+cmdb_ci_appl および製品別サブクラス
+cmdb_ci_server／各 OS サブクラス
+cmdb_ci_database／データベースサブクラス
+cmdb_ci_lb／ネットワーク・クラウドリソースのサブクラス
+【メンバーと実行時データ】
+svc_ci_assoc
+cmdb_rel_ci
+cmdb_running_process
+cmdb_tcp</x:v>
       </x:c>
       <x:c r="G23" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -1964,7 +2217,7 @@
         <x:v>https://www.servicenow.com/docs/r/it-operations-management/service-mapping/pattern-based-discovery.html?contentId=umMku4VDzCe1nsXChfx5Dg</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="64.5" customHeight="1">
+    <x:row r="24" ht="123" customHeight="1">
       <x:c r="A24" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -1981,8 +2234,17 @@
       <x:c r="E24" s="24" t="str">
         <x:v>ポータル アドレス、ポート、プロトコル、DNS、Web/アプリ ポータル、およびその関連サービス。</x:v>
       </x:c>
-      <x:c r="F24" s="24" t="str">
-        <x:v>通常、このエントリは cmdb_ci_service_discovered の開始点として機能します。テクニカル CI は、対応する cmdb_ci_appl/server/network サブクラスに書き込まれます。</x:v>
+      <x:c r="F24" s="188" t="str">
+        <x:v>【サービスレコード】
+cmdb_ci_service_discovered
+cmdb_ci_service_auto（親クラス／リリース依存）
+【入口に対応する技術 CI：Entry Point／Pattern に応じて関連】
+cmdb_ci_appl および製品別サブクラス
+cmdb_ci_lb
+cmdb_ci_ip_address
+cmdb_ci_dns_name
+cmdb_ci_server／データベース／クラウドリソースのサブクラス
+【関連】svc_ci_assoc、cmdb_rel_ci、cmdb_tcp</x:v>
       </x:c>
       <x:c r="G24" s="24" t="str">
         <x:v>svc_ci_assoc
@@ -2002,7 +2264,7 @@
         <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="64.5" customHeight="1">
+    <x:row r="25" ht="114" customHeight="1">
       <x:c r="A25" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2019,10 +2281,16 @@
       <x:c r="E25" s="24" t="str">
         <x:v>プロセス、リスニング ポート、ローカルおよびリモート接続、通信ピア。</x:v>
       </x:c>
-      <x:c r="F25" s="24" t="str">
-        <x:v>アプリケーションサービスを受け入れ/生成した後:
+      <x:c r="F25" s="188" t="str">
+        <x:v>【直接使用する実行時入力】
+cmdb_running_process
+cmdb_tcp
+【サービスの承認／生成後の対象】
 cmdb_ci_service_discovered
-cmdb_ci_service_auto</x:v>
+cmdb_ci_service_auto
+svc_ci_assoc
+cmdb_rel_ci
+注：TCP 通信の検出だけで必ず Application Service が生成されるわけではありません。機能の有効化、候補の承認、リリースに依存します。</x:v>
       </x:c>
       <x:c r="G25" s="24" t="str">
         <x:v>cmdb_tcp
@@ -2043,7 +2311,7 @@
         <x:v>https://www.servicenow.com/docs/r/washingtondc/it-operations-management/itom-visibility/r_DataCollDiscoTCPConnections.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="64.5" customHeight="1">
+    <x:row r="26" ht="96" customHeight="1">
       <x:c r="A26" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2060,8 +2328,15 @@
       <x:c r="E26" s="24" t="str">
         <x:v>送信元/宛先 IP、ポート、プロトコル、トラフィック、および時間枠は、潜在的な依存関係を検出するために使用されます。</x:v>
       </x:c>
-      <x:c r="F26" s="24" t="str">
-        <x:v>新しいインフラストラクチャ CI は通常、直接作成されません。マッピング結果は受け入れられ、cmdb_ci_service_discovered に関連付けられます。</x:v>
+      <x:c r="F26" s="188" t="str">
+        <x:v>【フローデータ入力】
+NetFlow／sFlow の生データまたは集約データテーブル（プラグイン／リリース固有。安定した共通 CMDB テーブルではありません）
+【照合／承認後の安定した CMDB 出力】
+cmdb_ci_service_discovered
+cmdb_ci_service_auto
+svc_ci_assoc
+cmdb_rel_ci
+既存の cmdb_ci_* メンバー CI</x:v>
       </x:c>
       <x:c r="G26" s="24" t="str">
         <x:v>プラグイン/バージョンによるトラフィック データ ストレージ テーブルの変更
@@ -2081,7 +2356,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/data-collected-by-itom-visibility.html?content-lang=en-US</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="64.5" customHeight="1">
+    <x:row r="27" ht="141" customHeight="1">
       <x:c r="A27" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2098,8 +2373,19 @@
       <x:c r="E27" s="24" t="str">
         <x:v>クラウド リソース間の送信元/宛先、ポート、プロトコル、許可/拒否、およびタイミング情報。</x:v>
       </x:c>
-      <x:c r="F27" s="24" t="str">
-        <x:v>通常は既存のクラウド cmdb_ci_* を再利用します。マッピング結果を受け入れ、cmdb_ci_service_discovered に関連付けます。</x:v>
+      <x:c r="F27" s="188" t="str">
+        <x:v>【クラウドフローログ入力】
+クラウドプロバイダーの VPC／VNet Flow Logs データテーブル（プラグイン／リリース固有）
+【再利用されるクラウドリソース CI】
+cmdb_ci_network
+cmdb_ci_cloud_subnet
+cmdb_ci_nic
+cmdb_ci_vm_instance
+cmdb_ci_cloud_load_balancer など
+【承認後のサービス出力】
+cmdb_ci_service_discovered
+svc_ci_assoc
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G27" s="24" t="str">
         <x:v>クラウド プロバイダーとプラグインのバージョンに応じてクラウド フロー ログ データ テーブルが変更される
@@ -2119,7 +2405,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/itom-visibility/cloud-discovery-collected-data.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="64.5" customHeight="1">
+    <x:row r="28" ht="105" customHeight="1">
       <x:c r="A28" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2136,9 +2422,15 @@
       <x:c r="E28" s="24" t="str">
         <x:v>タグキー値、ヒットクラウドリソース/CI、サービスメンバーシップ関係。</x:v>
       </x:c>
-      <x:c r="F28" s="24" t="str">
-        <x:v>cmdb_ci_service_by_tags
-さまざまな種類の cmdb_ci_* ヒット</x:v>
+      <x:c r="F28" s="188" t="str">
+        <x:v>【サービス対象】
+cmdb_ci_service_by_tags
+【タグとメンバー】
+cmdb_key_value
+svc_ci_assoc
+cmdb_rel_ci
+ルールに一致した各種 cmdb_ci_*
+注：メンバーは既存 CI から取得します。タグベースサービスはメンバーを構成するもので、基盤クラウドリソースを再作成しません。</x:v>
       </x:c>
       <x:c r="G28" s="24" t="str">
         <x:v>cmdb_key_value
@@ -2158,7 +2450,7 @@
         <x:v>https://www.servicenow.com/docs/r/it-operations-management/itom-visibility/itom-visibility-use-case.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="64.5" customHeight="1">
+    <x:row r="29" ht="96" customHeight="1">
       <x:c r="A29" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2175,9 +2467,14 @@
       <x:c r="E29" s="24" t="str">
         <x:v>サービス自体、選択されたメンバー CI、および関係。新しいインフラストラクチャ データは積極的に収集されません。</x:v>
       </x:c>
-      <x:c r="F29" s="24" t="str">
-        <x:v>cmdb_ci_service_manual
-既存の cmdb_ci_*</x:v>
+      <x:c r="F29" s="188" t="str">
+        <x:v>【サービス対象】
+cmdb_ci_service_manual
+【メンバーとリレーション】
+svc_ci_assoc
+cmdb_rel_ci
+手動で選択した既存の cmdb_ci_*
+注：これはサービスモデリングであり、インフラストラクチャのデータ収集ではありません。</x:v>
       </x:c>
       <x:c r="G29" s="24" t="str">
         <x:v>cmdb_rel_ci
@@ -2196,7 +2493,7 @@
         <x:v>https://www.servicenow.com/docs/r/it-operations-management/itom-visibility/itom-visibility-use-case.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="64.5" customHeight="1">
+    <x:row r="30" ht="132" customHeight="1">
       <x:c r="A30" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2213,11 +2510,18 @@
       <x:c r="E30" s="24" t="str">
         <x:v>通信グループ、候補メンバー、候補となる依存関係、信頼度。承認後に Application Service を作成します。</x:v>
       </x:c>
-      <x:c r="F30" s="24" t="str">
-        <x:v>受け入れられた後は、通常次のように書かれます。
+      <x:c r="F30" s="188" t="str">
+        <x:v>【候補生成段階の入力】
+cmdb_running_process
+cmdb_tcp
+cmdb_rel_ci
+既存の cmdb_ci_*
+【候補承認後の安定した出力】
 cmdb_ci_service_discovered
 cmdb_ci_service_auto
-既存の cmdb_ci_*</x:v>
+svc_ci_assoc
+cmdb_rel_ci
+注：候補／スコアリングの内部テーブルはリリースによって変わるため、安定したリリース横断のテーブル一覧には含めません。</x:v>
       </x:c>
       <x:c r="G30" s="24" t="str">
         <x:v>cmdb_running_process
@@ -2238,7 +2542,7 @@
         <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="64.5" customHeight="1">
+    <x:row r="31" ht="87" customHeight="1">
       <x:c r="A31" s="43" t="str">
         <x:v>Service Mapping
 （サービスマッピング）</x:v>
@@ -2255,9 +2559,13 @@
       <x:c r="E31" s="24" t="str">
         <x:v>リアルタイムでのクエリ定義とヒットした CI の収集。通常、新しい技術 CI は作成されません。</x:v>
       </x:c>
-      <x:c r="F31" s="24" t="str">
-        <x:v>cmdb_ci_query_based_service
-既存の cmdb_ci_*</x:v>
+      <x:c r="F31" s="188" t="str">
+        <x:v>【クエリベースサービスの対象】
+cmdb_ci_query_based_service
+【動的メンバー】
+クエリに一致した既存の cmdb_ci_*
+【条件付きで関連】
+svc_ci_assoc／cmdb_rel_ci（メンバーの表現方法はリリースとサービスタイプにより異なる）</x:v>
       </x:c>
       <x:c r="G31" s="24" t="str">
         <x:v>クエリとメンバーの関連はプラットフォームが動的に計算します。リレーションの表現はバージョンによって異なります。</x:v>
@@ -2275,7 +2583,7 @@
         <x:v>https://www.servicenow.com/docs/r/servicenow-platform/configuration-management-database-cmdb/application-services.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="64.5" customHeight="1">
+    <x:row r="32" ht="159" customHeight="1">
       <x:c r="A32" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2292,10 +2600,21 @@
       <x:c r="E32" s="24" t="str">
         <x:v>名前、RAM、製造元、model_id、CPU タイプ、OS/バージョン/ドメイン、IP、ゲートウェイ、シリアル番号、FQDN。</x:v>
       </x:c>
-      <x:c r="F32" s="24" t="str">
-        <x:v>一致したホスト CI (ci フィールドは実際のクラスを指します): 
+      <x:c r="F32" s="188" t="str">
+        <x:v>【照合／更新されるホスト CI】
+cmdb_ci
+cmdb_ci_hardware
 cmdb_ci_computer
-cmdb_ci_serverおよび OS サブクラス</x:v>
+cmdb_ci_server
+cmdb_ci_win_server／cmdb_ci_linux_server／その他の OS サブクラス
+【ACC 公式データ収集ページに記載された付随テーブル】
+cmdb_running_process
+cmdb_tcp
+cmdb_serial_number
+【データソース／重複排除／リレーション】
+sys_object_source
+cmdb_datasource_last_update
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G32" s="24" t="str">
         <x:v>cmdb_tcp
@@ -2315,7 +2634,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/acc-data-collection.html?contentId=XF2OUrZDVSv4nM40Vq66bg</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="64.5" customHeight="1">
+    <x:row r="33" ht="168" customHeight="1">
       <x:c r="A33" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2332,10 +2651,22 @@
       <x:c r="E33" s="24" t="str">
         <x:v>CPU メーカー／速度／数／コア／スレッド、OS アドレス幅、仮想フラグ、起動日時、object_id などを追加します。</x:v>
       </x:c>
-      <x:c r="F33" s="24" t="str">
-        <x:v>一致したホスト CI: 
+      <x:c r="F33" s="188" t="str">
+        <x:v>【拡張更新されるホスト CI】
+cmdb_ci
+cmdb_ci_hardware
 cmdb_ci_computer
-cmdb_ci_serverおよび OS サブクラス</x:v>
+cmdb_ci_server
+cmdb_ci_win_server／cmdb_ci_linux_server／その他の OS サブクラス
+【継続／拡張収集データ】
+cmdb_running_process
+cmdb_tcp
+cmdb_serial_number
+cmdb_ci_network_adapter／cmdb_ci_ip_address（対応コンテンツが有効な場合）
+【データソース／リレーション】
+sys_object_source
+cmdb_datasource_last_update
+cmdb_rel_ci</x:v>
       </x:c>
       <x:c r="G33" s="24" t="str">
         <x:v>cmdb_tcp
@@ -2356,7 +2687,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/acc-data-collection.html?contentId=XF2OUrZDVSv4nM40Vq66bg</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="64.5" customHeight="1">
+    <x:row r="34" ht="114" customHeight="1">
       <x:c r="A34" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2373,9 +2704,16 @@
       <x:c r="E34" s="24" t="str">
         <x:v>アプリケーション、バージョン、インストール/構成、プロセス、ポート、およびアプリケーションとホスト/データベース間の関係。</x:v>
       </x:c>
-      <x:c r="F34" s="24" t="str">
-        <x:v>cmdb_ci_appl および製品別サブクラス
-データベース、Middleware、Web Server などに対応する cmdb_ci_* を更新する場合もあります</x:v>
+      <x:c r="F34" s="188" t="str">
+        <x:v>【主要なアプリケーション対象】
+cmdb_ci_appl および ACC-VC Application Pattern で指定される製品別サブクラス
+【条件付きで関連する技術クラス】
+データベース、ミドルウェア、Web Server、Application Server に対応する cmdb_ci_* サブクラス
+cmdb_ci_computer／cmdb_ci_server
+cmdb_running_process
+cmdb_tcp
+cmdb_rel_ci
+注：固定された完全一覧はありません。インストール済み ACC-VC コンテンツパックと各 Pattern の Identification Section を基準に確認します。</x:v>
       </x:c>
       <x:c r="G34" s="24" t="str">
         <x:v>cmdb_running_process
@@ -2395,7 +2733,7 @@
         <x:v>https://www.servicenow.com/docs/r/it-operations-management/agent-client-collector/data-collection-enabling.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="98.25" customHeight="1">
+    <x:row r="35" ht="114" customHeight="1">
       <x:c r="A35" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2412,13 +2750,17 @@
       <x:c r="E35" s="24" t="str">
         <x:v>Java ファイル、バージョン、パス、プロセス、アプリケーション/コンピュータ参照、ソフトウェア インストールの証拠、および監査結果。</x:v>
       </x:c>
-      <x:c r="F35" s="24" t="str">
-        <x:v>ora_java_audit
-ora_java_evidence / cmdb_ora_java_evidence
+      <x:c r="F35" s="188" t="str">
+        <x:v>【Java 監査／エビデンス】
+ora_java_audit
+ora_java_evidence／cmdb_ora_java_evidence（対象インスタンスの実テーブル名を確認）
+【ソフトウェア／ファイル／アプリケーション／ホスト】
+cmdb_sam_sw_install
+cmdb_file_information
 cmdb_ci_appl
-cmdb_sam_sw_install
 cmdb_ci_computer
-cmdb_file_information</x:v>
+cmdb_ci
+cmdb_running_process</x:v>
       </x:c>
       <x:c r="G35" s="24" t="str">
         <x:v>cmdb_running_process
@@ -2437,7 +2779,7 @@
         <x:v>https://www.servicenow.com/docs/r/ja-JP/it-operations-management/agent-client-collector/data-collected-file-based-discovery.html?contentId=RY6KsW6LuAR9UUDY0y04iA</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="64.5" customHeight="1">
+    <x:row r="36" ht="87" customHeight="1">
       <x:c r="A36" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2454,10 +2796,14 @@
       <x:c r="E36" s="24" t="str">
         <x:v>証明書の件名/発行者、シリアル番号、フィンガープリント、有効期間、ポート、インストール場所、および CI の関連付け。</x:v>
       </x:c>
-      <x:c r="F36" s="24" t="str">
-        <x:v>cmdb_ci_certificate
+      <x:c r="F36" s="188" t="str">
+        <x:v>【証明書の主要テーブルと履歴】
+cmdb_ci_certificate
 sn_disco_certmgmt_certificate_history
-sn_disco_certmgmt_cmdb_installed_certificate</x:v>
+sn_disco_certmgmt_cmdb_installed_certificate
+【インストール対象／リレーション】
+対応するホスト、アプリケーション、ロードバランサーなどの cmdb_ci_*
+cmdb_rel_ci（具体的なリレーション表現はリリース／プラグインに依存）</x:v>
       </x:c>
       <x:c r="G36" s="24" t="str">
         <x:v>ホスト/アプリCIのインストールに関連付けられた証明書</x:v>
@@ -2475,7 +2821,7 @@
         <x:v>https://www.servicenow.com/docs/r/it-operations-management/agent-client-collector/run-cert-discovery-accvc.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="75.75" customHeight="1">
+    <x:row r="37" ht="114" customHeight="1">
       <x:c r="A37" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2492,8 +2838,15 @@
       <x:c r="E37" s="24" t="str">
         <x:v>インジケーターの時系列、可用性、しきい値/異常な結果。イベントとアラームは、イベント管理ルールを通じて生成できます。</x:v>
       </x:c>
-      <x:c r="F37" s="24" t="str">
-        <x:v>通常、新しい cmdb_ci_* アセットを作成するのではなく、既存の CI を更新/関連付けることが主な目標です。</x:v>
+      <x:c r="F37" s="188" t="str">
+        <x:v>【監視データ】
+Metric Store／Metric Intelligence で管理されるメトリクス時系列
+【イベントとアラート】
+em_event
+em_alert
+【コンテキスト】
+既存の cmdb_ci_*（関連付け。新規資産 CI の作成を主目的としない）
+注：メトリクスの物理テーブルはプラットフォーム実装で管理されます。顧客独自の直接参照インターフェースとしての利用は推奨しません。</x:v>
       </x:c>
       <x:c r="G37" s="24" t="str">
         <x:v>メトリック ストア/メトリック インテリジェンス データ
@@ -2514,7 +2867,7 @@
         <x:v>https://www.servicenow.com/docs/r/it-operations-management/agent-client-collector/configuring-agent-client-collector-monitoring.html?contentId=rBcYnlpdAm64rfXndUpnDA</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="64.5" customHeight="1">
+    <x:row r="38" ht="96" customHeight="1">
       <x:c r="A38" s="47" t="str">
         <x:v>ACC
 （Agent Client Collector）</x:v>
@@ -2531,8 +2884,14 @@
       <x:c r="E38" s="24" t="str">
         <x:v>ログ メッセージ、時刻、ソース ファイル/Windows イベント ログ、ホスト/アプリケーション コンテキスト、および監視対象の CI へのマップ。</x:v>
       </x:c>
-      <x:c r="F38" s="24" t="str">
-        <x:v>通常、新しい cmdb_ci_* は作成されません。既存の CI はロギング コンテキストとして再利用されます。</x:v>
+      <x:c r="F38" s="188" t="str">
+        <x:v>【ログデータパイプライン】
+Health Log Analytics で管理されるログストレージ／インデックス
+ACC data input／streaming source／log policy の関連レコード
+【コンテキスト】
+既存の cmdb_ci_*
+Dynamic CI Group（設定で使用する場合）
+注：ログは通常の cmdb_ci_* 資産テーブルには書き込まれません。物理インデックスと保持構造は HLA のリリースおよび設定で管理されます。</x:v>
       </x:c>
       <x:c r="G38" s="24" t="str">
         <x:v>Health Log Analytics のログ ストレージ/インデックス作成
@@ -2559,7 +2918,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b99aa9c810e47bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R023e6155099c4384"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5173,7 +5532,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raff78537a47f4180"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9ed426416194abe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6797,8 +7156,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b56b60d59da474c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a59e58d78454e49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6e7e4be9aff4859"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc97cbfd29434b24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7788,7 +8147,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref5bb0d927974d19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd161aeba8a2c4247"/>
   </x:tableParts>
 </x:worksheet>
 </file>